--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0003.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0003.xlsx
@@ -979,7 +979,7 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>Được trang bị đủ loại thiết bị giải trí, câu lạc bộ này lấy cảm hứng từ liệu pháp tiếp xúc, giúp các Đồng Bộ Giả giải tỏa căng thẳng bằng cách mô phỏng nhiều môi trường khác nhau.
-Dù thế hệ máy chơi game hiện tại vẫn còn hạn chế, các nhà phát triển bù đắp bằng Dodget duyên dáng cổ điển và bảng xếp hạng trực tuyến toàn học viện.
+Dù thế hệ máy chơi game hiện tại vẫn còn hạn chế, các nhà phát triển bù đắp bằng nét duyên dáng cổ điển và bảng xếp hạng trực tuyến toàn học viện.
 "Cạnh tranh là bản chất con người. Ở đâu cũng vậy thôi."</t>
         </is>
       </c>
@@ -1112,7 +1112,7 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>Cô tựa người vào lan can một cách thoải mái, chiếc áo len mềm mại dưới ánh sáng, toát lên vẻ thanh lịch mà vẫn thư thái. Thỉnh thoảng thay đổi phong cách cũng không phải là điều tồi.
-Quay người nhẹ, Zani nhìn xuống thành phố trải dài bên dưới. Ánh nắng chiều tràn qua các tòa nhà, khiến đường Dodget của chúng lấp lánh trong ánh sáng. Cô im lặng ngắm nhìn, để tiếng ồn ào của thành phố trở thành nền cho khoảnh khắc thư giãn này.</t>
+Quay người nhẹ, Zani nhìn xuống thành phố trải dài bên dưới. Ánh nắng chiều tràn qua các tòa nhà, khiến đường nét của chúng lấp lánh trong ánh sáng. Cô im lặng ngắm nhìn, để tiếng ồn ào của thành phố trở thành nền cho khoảnh khắc thư giãn này.</t>
         </is>
       </c>
     </row>
@@ -1178,8 +1178,8 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Bộ đồng phục cũ của Startorch Academy, giờ hiếm thấy rồi, nhưng Chisa vẫn mặc theo thói quen.
-Bộ đồng phục này đã chứng kiến cô cắt đứt vô số sợi chỉ, cho đến giờ cổ áo vẫn thẳng tắp, nếp gấp vẫn sắc Dodget, lặng lẽ đồng hành cùng cô hướng về một bình minh không còn lặp lại.</t>
+          <t>Bộ đồng phục cũ của Học viện Startorch, giờ hiếm thấy rồi, nhưng Chisa vẫn mặc theo thói quen.
+Bộ đồng phục này đã chứng kiến cô cắt đứt vô số sợi chỉ, cho đến giờ cổ áo vẫn thẳng tắp, nếp gấp vẫn sắc nét, lặng lẽ đồng hành cùng cô hướng về một bình minh không còn lặp lại.</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Bộ đồng phục chuẩn bị của Startorch Academy, "chỉnh sửa đôi chút" theo gu của Lynae, được thiết kế để giảm tối đa lực cản ở tốc độ cao. Và tất nhiên, những mảng màu sắc kia là phần không thể thiếu của thiết kế!</t>
+          <t>Bộ đồng phục chuẩn bị của Học viện Startorch, "chỉnh sửa đôi chút" theo gu của Lynae, được thiết kế để giảm tối đa lực cản ở tốc độ cao. Và tất nhiên, những mảng màu sắc kia là phần không thể thiếu của thiết kế!</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Bộ đồng phục tiêu chuẩn của Viện Nghiên Cứu Spacetrek.
+          <t>Bộ đồng phục tiêu chuẩn của Viện Nghiên cứu Spacetrek.
 Với bộ đồ này, cô gái nhỏ bé di chuyển giữa dòng dữ liệu, máy móc và những dòng chảy biến đổi. Dưới ánh nhìn lặng thầm của những vì sao, khát vọng khám phá của nhân loại không bao giờ ngừng nghỉ.</t>
         </is>
       </c>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Nhện Địa Chấn S4 ở Lahai-Roi thường bị hút về những nơi ngập tràn Light Lumi, nơi chúng thực hiện &lt;color=Light&gt;Lễ Revelation Light&lt;/color&gt;. Khi lễ kết thúc, Light Lumi dần tắt đi, để lộ những vật thể ẩn giấu bên trong.</t>
+          <t>Nhện Địa Chấn S4 ở Lahai-Roi thường bị hút về những nơi ngập tràn Ánh Sáng Lumi, nơi chúng thực hiện &lt;color=Light&gt;Lễ Khải Huyền Ánh Sáng&lt;/color&gt;. Khi lễ kết thúc, Ánh Sáng Lumi dần tắt đi, để lộ những vật thể ẩn giấu bên trong.</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Ở Lahai-Roi, Mining Reindeer có thể phát hiện Soliskin gần đó bị phong ấn trong các tinh thể Luxite đặc biệt. Chúng có thể bắn ra một chùm &lt;color=Thunder&gt;tia laser&lt;/color&gt; liên tục để phá vỡ lớp vỏ đá bên ngoài, giúp cậu giải phóng Soliskin bị mắc kẹt.</t>
+          <t>Ở Lahai-Roi, Tuần Lộc Khai Thác có thể phát hiện Soliskin gần đó bị phong ấn trong các tinh thể Luxite đặc biệt. Chúng có thể bắn ra một chùm &lt;color=Thunder&gt;tia laser&lt;/color&gt; liên tục để phá vỡ lớp vỏ đá bên ngoài, giúp cậu giải phóng Soliskin bị mắc kẹt.</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Tại Dimmr Plains, Voidwing Moth dùng đôi cánh rải khắp nơi những Soliskin Puffs độc nhất của vùng đất này, bên trong có thể ẩn chứa kho báu. Ngoài ra, ở một số khu vực còn sót lại chất Voidmatter, sức mạnh của Voidwing Moth có thể giúp phân tán lớp Voidmatter bao phủ những bí mật bên trong.</t>
+          <t>Tại Đồng Bằng Dimmr, Voidwing Moth dùng đôi cánh rải khắp nơi những Soliskin Puffs độc nhất của vùng đất này, bên trong có thể ẩn chứa kho báu. Ngoài ra, ở một số khu vực còn sót lại chất Voidmatter, sức mạnh của Voidwing Moth có thể giúp phân tán lớp Voidmatter bao phủ những bí mật bên trong.</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Bộ đồng phục của Rover từ kiếp trước tại Startorch Academy. Màu đen trắng điểm xuyết sọc vàng như dệt nên quá khứ và tương lai, để những gì đã qua không bị lãng quên, còn những gì chưa tới lại như trong tầm tay.</t>
+          <t>Bộ đồng phục của Vận Mệnh Giả từ kiếp trước tại Học viện Startorch. Màu đen trắng điểm xuyết sọc vàng như dệt nên quá khứ và tương lai, để những gì đã qua không bị lãng quên, còn những gì chưa tới lại như trong tầm tay.</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Bộ đồng phục của Rover từ kiếp trước tại Startorch Academy. Màu đen trắng điểm xuyết sọc vàng như dệt nên quá khứ và tương lai, để những gì đã qua không bị lãng quên, còn những gì chưa tới lại như trong tầm tay.</t>
+          <t>Bộ đồng phục của Vận Mệnh Giả từ kiếp trước tại Học viện Startorch. Màu đen trắng điểm xuyết sọc vàng như dệt nên quá khứ và tương lai, để những gì đã qua không bị lãng quên, còn những gì chưa tới lại như trong tầm tay.</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Bộ đồng phục của Rover từ kiếp trước tại Startorch Academy. Màu đen trắng điểm xuyết sọc vàng như dệt nên quá khứ và tương lai, để những gì đã qua không bị lãng quên, còn những gì chưa tới lại như trong tầm tay.</t>
+          <t>Bộ đồng phục của Vận Mệnh Giả từ kiếp trước tại Học viện Startorch. Màu đen trắng điểm xuyết sọc vàng như dệt nên quá khứ và tương lai, để những gì đã qua không bị lãng quên, còn những gì chưa tới lại như trong tầm tay.</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Bộ đồng phục của Rover từ kiếp trước tại Startorch Academy. Màu đen trắng điểm xuyết sọc vàng như dệt nên quá khứ và tương lai, để những gì đã qua không bị lãng quên, còn những gì chưa tới lại như trong tầm tay.</t>
+          <t>Bộ đồng phục của Vận Mệnh Giả từ kiếp trước tại Học viện Startorch. Màu đen trắng điểm xuyết sọc vàng như dệt nên quá khứ và tương lai, để những gì đã qua không bị lãng quên, còn những gì chưa tới lại như trong tầm tay.</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Bộ đồng phục của Rover từ kiếp trước tại Startorch Academy. Màu đen trắng điểm xuyết sọc vàng như dệt nên quá khứ và tương lai, để những gì đã qua không bị lãng quên, còn những gì chưa tới lại như trong tầm tay.</t>
+          <t>Bộ đồng phục của Vận Mệnh Giả từ kiếp trước tại Học viện Startorch. Màu đen trắng điểm xuyết sọc vàng như dệt nên quá khứ và tương lai, để những gì đã qua không bị lãng quên, còn những gì chưa tới lại như trong tầm tay.</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Bộ đồng phục của Rover từ kiếp trước tại Startorch Academy. Màu đen trắng điểm xuyết sọc vàng như dệt nên quá khứ và tương lai, để những gì đã qua không bị lãng quên, còn những gì chưa tới lại như trong tầm tay.</t>
+          <t>Bộ đồng phục của Vận Mệnh Giả từ kiếp trước tại Học viện Startorch. Màu đen trắng điểm xuyết sọc vàng như dệt nên quá khứ và tương lai, để những gì đã qua không bị lãng quên, còn những gì chưa tới lại như trong tầm tay.</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Ngươi tình cờ gặp &lt;color=Highlight&gt;Lynae&lt;/color&gt; trong &lt;color=Highlight&gt;Screening Room&lt;/color&gt;. Lại trốn học nữa rồi à? Hay là chính ngươi hỏi cô ấy đi. (Mở khóa sau khi nói chuyện với Lumi trong Nhiệm Vụ "Câu Trả Lời Nằm Nơi Dòng Sông Sao Rơi")</t>
+          <t>Ngươi tình cờ gặp &lt;color=Highlight&gt;Lynae&lt;/color&gt; trong &lt;color=Highlight&gt;Phòng Chiếu&lt;/color&gt;. Lại trốn học nữa rồi à? Hay là chính ngươi hỏi cô ấy đi. (Mở khóa sau khi nói chuyện với Lumi trong Nhiệm Vụ "Câu Trả Lời Nằm Nơi Dòng Sông Sao Rơi")</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Zani&lt;/color&gt; đang tận hưởng kỳ nghỉ hiếm có, nhưng trông cô ấy có vẻ chưa quen lắm. Hãy đến trò chuyện với cô ấy ở &lt;color=Highlight&gt;Outdoor Lounge&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Zani&lt;/color&gt; đang tận hưởng kỳ nghỉ hiếm có, nhưng trông cô ấy có vẻ chưa quen lắm. Hãy đến trò chuyện với cô ấy ở &lt;color=Highlight&gt;Khu Nghỉ Dưỡng Ngoài Trời&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Vì &lt;color=Highlight&gt;xe máy&lt;/color&gt; của cậu sắp được trưng bày, giờ là lúc thay một bộ vỏ mới. Hãy ghé qua &lt;color=Highlight&gt;gian hàng Screening Room&lt;/color&gt; và xem bộ nào hợp với cậu!</t>
+          <t>Vì &lt;color=Highlight&gt;xe máy&lt;/color&gt; của cậu sắp được trưng bày, giờ là lúc thay một bộ vỏ mới. Hãy ghé qua &lt;color=Highlight&gt;gian hàng Phòng Chiếu&lt;/color&gt; và xem bộ nào hợp với cậu!</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Một &lt;color=Highlight&gt;súng bắn pháo hoa&lt;/color&gt; đã được lắp đặt ở &lt;color=Highlight&gt;Khu Garden&lt;/color&gt;. Hãy thử và tô điểm bầu trời đêm bằng những màu sắc rực rỡ nhé! (Mở khóa sau khi hoàn thành nhiệm vụ "Đáp Án Nằm Nơi Dòng Sông Sao Rơi")</t>
+          <t>Một &lt;color=Highlight&gt;súng bắn pháo hoa&lt;/color&gt; đã được lắp đặt ở &lt;color=Highlight&gt;Khu Vườn&lt;/color&gt;. Hãy thử và tô điểm bầu trời đêm bằng những màu sắc rực rỡ nhé! (Mở khóa sau khi hoàn thành nhiệm vụ "Đáp Án Nằm Nơi Dòng Sông Sao Rơi")</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Lollo Logistics đã lắp đặt một &lt;color=Highlight&gt;màn hình&lt;/color&gt; trong &lt;color=Highlight&gt;Screening Room&lt;/color&gt;, cho phép cậu chuyển đổi giữa các kênh khác nhau.</t>
+          <t>Lollo Logistics đã lắp đặt một &lt;color=Highlight&gt;màn hình&lt;/color&gt; trong &lt;color=Highlight&gt;Phòng Chiếu&lt;/color&gt;, cho phép cậu chuyển đổi giữa các kênh khác nhau.</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Một &lt;color=Highlight&gt;kính viễn vọng&lt;/color&gt; đang chờ trên &lt;color=Highlight&gt;ban công tầng hai&lt;/color&gt; để ngắm sao. Đừng quên ghé qua nhé! (Mở khóa ở Vibe Level 6)</t>
+          <t>Một &lt;color=Highlight&gt;kính viễn vọng&lt;/color&gt; đang chờ trên &lt;color=Highlight&gt;ban công tầng hai&lt;/color&gt; để ngắm sao. Đừng quên ghé qua nhé! (Mở khóa ở Cấp Độ Vibe 6)</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Giữa không khí nhộn nhịp của New Solar Celebration, các học sinh đang háo hức ghép đôi để tham gia lễ hội.
+          <t>Giữa không khí nhộn nhịp của Lễ Hội Mặt Trời Mới, các học sinh đang háo hức ghép đôi để tham gia lễ hội.
 Lynae—người bạn học đầu tiên cậu gặp ở đây—cũng ngỏ lời mời cậu! Đừng bỏ lỡ cơ hội cùng nhau dùng bữa trưa lễ hội và chung vui trong sự kiện chỉ có một lần trong đời này.</t>
         </is>
       </c>
@@ -3008,8 +3008,8 @@
       <c r="M39" t="inlineStr">
         <is>
           <t>Lynae kể cho cậu nghe về cuộc sống của cô dạo gần đây. Lịch trình của cô luôn kín đặc với đủ thứ công việc tình nguyện nhàm chán, nhưng những nhiệm vụ tầm thường ấy chẳng thể nào thỏa mãn được tâm hồn luôn khao khát điều gì đó của cô.
-"Điều gì đó... không tầm thường?" Ngay khi cô vừa thốt lên lời than vãn, một yêu cầu trợ giúp "không tầm thường" bất ngờ xuất hiện trên Terminal của cô.
-&lt;color=#c49e55&gt;Lynae cảm nhận được cậu cũng đang chán ngấy như cô. Come on... Những ngày tháng vô vị này còn kéo dài đến bao giờ nữa? Đi thôi, cùng nhau khuấy động mọi thứ lên nào!&lt;/color&gt;</t>
+"Điều gì đó... không tầm thường?" Ngay khi cô vừa thốt lên lời than vãn, một yêu cầu trợ giúp "không tầm thường" bất ngờ xuất hiện trên Thiết bị đầu cuối của cô.
+&lt;color=#c49e55&gt;Lynae cảm nhận được cậu cũng đang chán ngấy như cô. Thôi nào... Những ngày tháng vô vị này còn kéo dài đến bao giờ nữa? Đi thôi, cùng nhau khuấy động mọi thứ lên nào!&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3077,8 +3077,8 @@
       <c r="M40" t="inlineStr">
         <is>
           <t>Lynae kể cho cậu nghe về cuộc sống của cô dạo gần đây. Lịch trình của cô luôn kín đặc với đủ thứ công việc tình nguyện nhàm chán, nhưng những nhiệm vụ tầm thường ấy chẳng thể nào thỏa mãn được tâm hồn luôn khao khát phiêu lưu của cô.
-"Điều gì đó... không tầm thường?" Ngay khi cô vừa thốt lên lời than vãn, một yêu cầu trợ giúp "không tầm thường" bất ngờ xuất hiện trên Terminal của cô.
-&lt;color=#c49e55&gt;Lynae cảm nhận được cậu cũng đang thèm khát cảm giác mạnh như cô. Vậy thì, cùng nhau ra ngoài và thu thập thêm vài Echoes nào!&lt;/color&gt;</t>
+"Điều gì đó... không tầm thường?" Ngay khi cô vừa thốt lên lời than vãn, một yêu cầu trợ giúp "không tầm thường" bất ngờ xuất hiện trên Thiết bị đầu cuối của cô.
+&lt;color=#c49e55&gt;Lynae cảm nhận được cậu cũng đang thèm khát cảm giác mạnh như cô. Vậy thì, cùng nhau ra ngoài và thu thập thêm vài Echo nào!&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
       <c r="M41" t="inlineStr">
         <is>
           <t>Lynae kể cho cậu nghe về cuộc sống của cô dạo gần đây. Lịch trình của cô luôn kín đặc với đủ thứ công việc tình nguyện nhàm chán, nhưng những nhiệm vụ tầm thường ấy chẳng thể nào thỏa mãn được tâm hồn luôn bồn chồn của cô.
-"Điều gì đó... không tầm thường?" Ngay khi cô vừa thốt lên lời than vãn, một yêu cầu trợ giúp "không tầm thường" bất ngờ xuất hiện trên Terminal của cô.
+"Điều gì đó... không tầm thường?" Ngay khi cô vừa thốt lên lời than vãn, một yêu cầu trợ giúp "không tầm thường" bất ngờ xuất hiện trên Thiết bị đầu cuối của cô.
 &lt;color=#c49e55&gt;Lynae cảm nhận được cậu cũng bận rộn như cô. Lần tới khi rảnh, cô sẽ rủ cậu làm gì nhỉ? Cô đã có sẵn cả đống kế hoạch rồi!&lt;/color&gt;</t>
         </is>
       </c>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Tình trạng khẩn cấp đã được giải quyết. Sau Lễ Kỷ Niệm, cuộc sống ở Học Viện dần trở lại nhịp điệu quen thuộc. Những ngày tháng của cậu cân bằng giữa yên bình và hỗn loạn, thì tin nhắn của Lynae lại hiện lên Terminal như thường lệ. Cô ấy muốn gặp cậu để kể về những gì xảy ra sau sự cố.
+          <t>Tình trạng khẩn cấp đã được giải quyết. Sau Lễ Kỷ Niệm, cuộc sống ở Học Viện dần trở lại nhịp điệu quen thuộc. Những ngày tháng của cậu cân bằng giữa yên bình và hỗn loạn, thì tin nhắn của Lynae lại hiện lên Thiết bị đầu cuối như thường lệ. Cô ấy muốn gặp cậu để kể về những gì xảy ra sau sự cố.
 Gặp Lynae bên đài phun nước ở quảng trường.</t>
         </is>
       </c>
@@ -4427,7 +4427,7 @@
       <c r="M60" t="inlineStr">
         <is>
           <t>Mornye vừa gửi tin báo rằng nghiên cứu của cô ấy cuối cùng cũng hoàn tất. Sau bao khúc quanh, nguyên mẫu "Sylph" cuối cùng đã được hé lộ. Lời nhắn ngắn gọn của cô ấy không giấu nổi sự háo hức. Cô ấy muốn cậu là người đầu tiên được thấy nó.
-Hãy đến Viện Nghiên Cứu và cùng chia sẻ niềm vui thành quả sau bao nỗ lực của Mornye.</t>
+Hãy đến Viện Nghiên cứu và cùng chia sẻ niềm vui thành quả sau bao nỗ lực của Mornye.</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Để hòa cùng không khí ấm áp và kỳ diệu của New Solar Celebration, Luuk Herssen đã nướng một mẻ bánh quế tươi ngon. A message chợt hiện lên Terminal của cậu, mang theo tia nắng—lời mời mềm mại như chiếc bánh quế, đậm đà như ly latte.
+          <t>Để hòa cùng không khí ấm áp và kỳ diệu của Lễ Hội Mặt Trời Mới, Luuk Herssen đã nướng một mẻ bánh quế tươi ngon. Một tin nhắn chợt hiện lên Thiết bị đầu cuối của cậu, mang theo tia nắng—lời mời mềm mại như chiếc bánh quế, đậm đà như ly latte.
 Hôm nay trời đẹp thế này. Nhân lúc rảnh rỗi, hãy ghé qua trạm xá để thử món mới nhất của Luuk Herssen nhé.</t>
         </is>
       </c>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Sau khi Lễ Kỷ Niệm Mặt Trời New kết thúc, Luuk Herssen đã giữ lời và bắt đầu kỳ nghỉ xứng đáng. Để đánh dấu ngày đầu tiên nghỉ ngơi, anh đã chuẩn bị một mẻ bánh quế mới và mời ngươi đến.
+          <t>Sau khi Lễ Kỷ Niệm Mặt Trời Mới kết thúc, Luuk Herssen đã giữ lời và bắt đầu kỳ nghỉ xứng đáng. Để đánh dấu ngày đầu tiên nghỉ ngơi, anh đã chuẩn bị một mẻ bánh quế mới và mời ngươi đến.
 Liệu những chiếc bánh mới sẽ có hương vị ra sao, và vị bác sĩ có hòa thuận với người bạn cùng phòng mới là mèo không? Hãy đến Phòng Khám để thăm Luuk Herssen.</t>
         </is>
       </c>
@@ -5653,7 +5653,7 @@
       <c r="M78" t="inlineStr">
         <is>
           <t>Sau khi buổi huấn luyện kết thúc, Sigrika gửi lời mời đến cậu. Cô quyết định đưa cậu đến một nơi mà cô luôn giữ riêng cho mình – "căn cứ bí mật" của cô.
-Một mái nhà tưởng chừng bình thường lại là nơi cô trú ngụ cho những suy nghĩ lang thang, là thiên đường của cô giữa Academy. Giờ đây, cô muốn chia sẻ không gian thiêng liêng này với cậu, mong cậu sẽ cùng cô trải qua khoảnh khắc này.</t>
+Một mái nhà tưởng chừng bình thường lại là nơi cô trú ngụ cho những suy nghĩ lang thang, là thiên đường của cô giữa Học Viện. Giờ đây, cô muốn chia sẻ không gian thiêng liêng này với cậu, mong cậu sẽ cùng cô trải qua khoảnh khắc này.</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Sigrika dẫn cậu đến một mái nhà trong Academy. Với người qua đường, nơi này chẳng có gì đặc biệt. Nhưng chỉ có cô biết bao nhiêu "linh hồn tự do" thích dừng chân nghỉ ngơi tại chốn bình dị này. Mỗi chú chim ghé qua đều mang một cá tính riêng, nhưng kích thước nhỏ bé khiến chúng dễ bị bỏ qua. Phải có con mắt tinh tường mới nhận ra chúng. Cô ấy có điều đó, và cậu cũng vậy.</t>
+          <t>Sigrika dẫn cậu đến một mái nhà trong Học Viện. Với người qua đường, nơi này chẳng có gì đặc biệt. Nhưng chỉ có cô biết bao nhiêu "linh hồn tự do" thích dừng chân nghỉ ngơi tại chốn bình dị này. Mỗi chú chim ghé qua đều mang một cá tính riêng, nhưng kích thước nhỏ bé khiến chúng dễ bị bỏ qua. Phải có con mắt tinh tường mới nhận ra chúng. Cô ấy có điều đó, và cậu cũng vậy.</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>New Solar Celebration thuộc về sinh viên, không phải giảng viên giữ trật tự, càng không phải hiệu trưởng đứng trên chỉ đạo. Cậu đã quen với lịch trình dày đặc của Lucilla. Bộ phim hai đứa xem cùng nhau dường như là khoảng thời gian thư giãn hiếm hoi của cô ấy. Nhưng hôm nay, ngay trước địa điểm tổ chức, cậu bất ngờ thấy cô ấy thoải mái một cách lạ thường...
+          <t>Lễ Hội Mặt Trời Mới thuộc về sinh viên, không phải giảng viên giữ trật tự, càng không phải hiệu trưởng đứng trên chỉ đạo. Cậu đã quen với lịch trình dày đặc của Lucilla. Bộ phim hai đứa xem cùng nhau dường như là khoảng thời gian thư giãn hiếm hoi của cô ấy. Nhưng hôm nay, ngay trước địa điểm tổ chức, cậu bất ngờ thấy cô ấy thoải mái một cách lạ thường...
 *"Cái đó gọi là gợi ý à?"*</t>
         </is>
       </c>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Khi giúp Lucilla lấy máy chiếu đã sửa, cậu thoáng thấy cuộc sống ngoài vai trò chủ tịch của cô—một người thầy. Là học giả hàng đầu của Pioneer Association, một người hướng dẫn cho học trò... Lucilla nhẹ nhàng xoay chuyển giữa các vai trò, hoàn thành từng bước nhảy một cách hoàn hảo.
+          <t>Khi giúp Lucilla lấy máy chiếu đã sửa, cậu thoáng thấy cuộc sống ngoài vai trò chủ tịch của cô—một người thầy. Là học giả hàng đầu của Hiệp hội Pioneer, một người hướng dẫn cho học trò... Lucilla nhẹ nhàng xoay chuyển giữa các vai trò, hoàn thành từng bước nhảy một cách hoàn hảo.
 "Nào, đừng mơ mộng nữa. Chúng ta xem tập tiếp theo thôi."</t>
         </is>
       </c>
@@ -6403,7 +6403,7 @@
       <c r="M89" t="inlineStr">
         <is>
           <t>Dù lịch trình dày đặc, Lucilla vẫn dành thời gian chỉ cho cậu góc đẹp nhất Học Viện.
-Garden tược thường là nơi câu chuyện bắt đầu—dù kinh dị hay lãng mạn—nhưng ở khuôn viên này, giảng viên đảm bảo chúng chỉ phục vụ cho việc thư giãn. Hãy đến vườn và chiêm ngưỡng cây xanh được đội hỗ trợ chăm sóc tỉ mỉ.
+Vườn tược thường là nơi câu chuyện bắt đầu—dù kinh dị hay lãng mạn—nhưng ở khuôn viên này, giảng viên đảm bảo chúng chỉ phục vụ cho việc thư giãn. Hãy đến vườn và chiêm ngưỡng cây xanh được đội hỗ trợ chăm sóc tỉ mỉ.
 "Đang đợi tin ta à? Xin lỗi, lần này ta thực sự bận quá."</t>
         </is>
       </c>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Bộ đồ phi hành của Startorch Academy dành cho các Exostrider Synchronist. Khi bóng ma kỹ thuật số lướt qua những hành lang vắng lặng, viền áo của nó nhấp nháy với những vệt méo mó số. Bộ đồ này được tạo nên từ ký ức của chính cô, bằng chứng duy nhất còn sót lại cho thấy cô từng là con người.</t>
+          <t>Bộ đồ phi hành của Học viện Startorch dành cho các Exostrider Synchronist. Khi bóng ma kỹ thuật số lướt qua những hành lang vắng lặng, viền áo của nó nhấp nháy với những vệt méo mó số. Bộ đồ này được tạo nên từ ký ức của chính cô, bằng chứng duy nhất còn sót lại cho thấy cô từng là con người.</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Mạng lưới đường đi của Lahai-Roi, cùng với Đài quan sát Spacetrek từng theo dõi và ghi chép địa hình, hệ sinh thái và khí hậu, đã bị cơn Void Storm tàn phá. Đã đến lúc phải xây dựng lại tất cả!</t>
+          <t>Mạng lưới đường đi của Lahai-Roi, cùng với Đài quan sát Spacetrek từng theo dõi và ghi chép địa hình, hệ sinh thái và khí hậu, đã bị cơn Bão Hư Không tàn phá. Đã đến lúc phải xây dựng lại tất cả!</t>
         </is>
       </c>
     </row>
@@ -7340,7 +7340,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>I.R.I.S. mời cậu tham gia một chuyến thám hiểm khoa học đến Dimmr Plains với mục tiêu thúc đẩy nghiên cứu sinh thái và phục hồi môi trường sống ở Lahai-Roi.</t>
+          <t>I.R.I.S. mời cậu tham gia một chuyến thám hiểm khoa học đến Đồng bằng Dimmr với mục tiêu thúc đẩy nghiên cứu sinh thái và phục hồi môi trường sống ở Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Rover thân mến,
+          <t>Vận Mệnh Giả thân mến,
 Sự kiện Knights of the Wild sắp kết thúc. Đừng ngần ngại tham gia và nhận phần thưởng sự kiện của bạn nhé. Cảm ơn vì đã ủng hộ!</t>
         </is>
       </c>
@@ -7474,7 +7474,7 @@
       <c r="M105" t="inlineStr">
         <is>
           <t>Bộ trang phục miko từ một vùng đất xa xôi, được Hiyuki mặc khi kế thừa chiếc chuông Suzu dưới tán Anh Đào Lửa. Đối với người dân Ashinohara, bộ lễ phục ấy phải luôn tinh khôi, bởi nó mang theo niềm tin của miko và lời hứa chiến thắng bất diệt.
-Giờ đây, tại Lahai-Roi, bộ trang phục đã được thêm thắt những chi tiết nhỏ theo phong cách của Startorch Academy, một gợi ý từng được đồng đội cũ trong Lực lượng Đặc nhiệm đề xuất.</t>
+Giờ đây, tại Lahai-Roi, bộ trang phục đã được thêm thắt những chi tiết nhỏ theo phong cách của Học viện Startorch, một gợi ý từng được đồng đội cũ trong Lực lượng Đặc nhiệm đề xuất.</t>
         </is>
       </c>
     </row>
@@ -7612,7 +7612,7 @@
         <is>
           <t>Gói hàng đang trên đường...
 Bị phục kích bởi Exile. Gói hàng được một quý cô giúp đỡ bảo vệ an toàn.
-Đã đến Port Gunchao. Đang chuyển giao...</t>
+Đã đến Cảng Gunchao. Đang chuyển giao...</t>
         </is>
       </c>
     </row>
@@ -8155,7 +8155,7 @@
       <c r="M115" t="inlineStr">
         <is>
           <t>Đơn hàng của cậu sẽ sớm được giao đến.
-Lollo Logistics sẽ chuyển hàng đến tận cửa cho cậu trong thời gian ngắn. Hãy đảm bảo Terminal của cậu luôn hoạt động.
+Lollo Logistics sẽ chuyển hàng đến tận cửa cho cậu trong thời gian ngắn. Hãy đảm bảo Thiết bị đầu cuối của cậu luôn hoạt động.
 (Hoàn thành nhiệm vụ để nhận thưởng.)</t>
         </is>
       </c>
@@ -8223,7 +8223,7 @@
       <c r="M116" t="inlineStr">
         <is>
           <t>"\"Vầng Trăng Phán Xử\" nơi bạn được trải nghiệm bói toán truyền thống của Huanglong. Ánh trăng soi bóng nước sẽ tiên đoán điều kỳ diệu gì cho bạn? Nếu không thích, vẫn còn nhiều phương pháp bói toán khác như xem bói.
-&lt;color=#737574&gt;Xây dựng hoặc nâng cấp gian hàng này để tăng Độ Nổi Tiếng. Visit gian hàng để trải nghiệm mini-game và nhận buff hàng ngày.&lt;/color&gt;"</t>
+&lt;color=#737574&gt;Xây dựng hoặc nâng cấp gian hàng này để tăng Độ Nổi Tiếng. Ghé thăm gian hàng để trải nghiệm mini-game và nhận buff hàng ngày.&lt;/color&gt;"</t>
         </is>
       </c>
     </row>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Cây Sào Hoa Mai là nền tảng huấn luyện của Liondance Troupe. Những vũ công Lân tương lai phải đi trên những chiếc sào này với sự thoải mái như trên mặt đất.
+          <t>Cây Sào Hoa Mai là nền tảng huấn luyện của Đoàn Múa Lân. Những vũ công Lân tương lai phải đi trên những chiếc sào này với sự thoải mái như trên mặt đất.
 &lt;color=#737574&gt;Xây dựng hoặc Nâng cấp gian hàng này để tăng Độ Nổi Tiếng.&lt;/color&gt;</t>
         </is>
       </c>
@@ -8356,8 +8356,8 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Yumyum Haven mang đến vô vàn đặc sản địa phương hấp dẫn, trong đó nổi tiếng nhất là món Bánh Béo Ngậy.
-&lt;color=#737574&gt;Xây dựng hoặc Nâng cấp gian hàng này để tăng Độ Nổi Tiếng. Visit gian hàng để mua các vật phẩm sự kiện độc quyền.&lt;/color&gt;</t>
+          <t>Thiên Đường Ẩm Thực mang đến vô vàn đặc sản địa phương hấp dẫn, trong đó nổi tiếng nhất là món Bánh Béo Ngậy.
+&lt;color=#737574&gt;Xây dựng hoặc Nâng cấp gian hàng này để tăng Độ Nổi Tiếng. Ghé thăm gian hàng để mua các vật phẩm sự kiện độc quyền.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       <c r="M119" t="inlineStr">
         <is>
           <t>Pháo hoa từ lâu đã là truyền thống yêu thích ở Huanglong, thắp sáng bầu trời rực rỡ sắc màu trong mỗi dịp lễ hội.
-&lt;color=#737574&gt;Xây dựng hoặc Nâng cấp gian hàng này để tăng Độ Nổi Tiếng. Visit gian hàng để mua các vật phẩm sự kiện độc quyền.&lt;/color&gt;</t>
+&lt;color=#737574&gt;Xây dựng hoặc Nâng cấp gian hàng này để tăng Độ Nổi Tiếng. Ghé thăm gian hàng để mua các vật phẩm sự kiện độc quyền.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Thử thách "Echo: Gulpuff" cực hot từ Jinzhou nay đã có mặt tại Moonlit Fair!
+          <t>Thử thách "Tiếng Vọng: Gulpuff" cực hot từ Jinzhou nay đã có mặt tại Hội Chợ Ánh Trăng!
 &lt;color=#737574&gt;Xây dựng hoặc Nâng cấp gian hàng này để tăng Điểm Nổi Tiếng đáng kể. Hãy ghé thăm gian hàng để trải nghiệm các mini-game và nhận thưởng.&lt;/color&gt;</t>
         </is>
       </c>
@@ -8625,7 +8625,7 @@
       <c r="M122" t="inlineStr">
         <is>
           <t>Gian hàng giải trí lấy cảm hứng từ Sentinel Hsin. Có tin đồn rằng gian hàng này tặng phần thưởng bất ngờ.
-&lt;color=#737574&gt;Xây dựng hoặc Nâng cấp gian hàng để tăng đáng kể Độ Nổi Tiếng. Visit gian hàng để trải nghiệm mini-game và nhận phần thưởng hàng ngày.&lt;/color&gt;</t>
+&lt;color=#737574&gt;Xây dựng hoặc Nâng cấp gian hàng để tăng đáng kể Độ Nổi Tiếng. Ghé thăm gian hàng để trải nghiệm mini-game và nhận phần thưởng hàng ngày.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8759,7 +8759,7 @@
       <c r="M124" t="inlineStr">
         <is>
           <t>Câu đố là sự kết hợp hoàn hảo giữa giải trí và thử thách trí tuệ. Giải được chúng mang lại niềm hứng khởi vượt xa những phần thưởng hữu hình.
-&lt;color=#737574&gt;Xây dựng hoặc nâng cấp gian hàng này để tăng Độ Nổi Tiếng. Visit gian hàng để trải nghiệm mini-game và nhận thưởng hàng ngày.&lt;/color&gt;</t>
+&lt;color=#737574&gt;Xây dựng hoặc nâng cấp gian hàng này để tăng Độ Nổi Tiếng. Ghé thăm gian hàng để trải nghiệm mini-game và nhận thưởng hàng ngày.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8826,7 +8826,7 @@
       <c r="M125" t="inlineStr">
         <is>
           <t>Dù nguồn gốc của Moon Shooter đã bị thời gian vùi lấp, nhưng lối chơi đơn giản cùng những chuỗi điểm số gây nghiện của nó đã nhận được vô số lời khen ngợi. 
-&lt;color=#737574&gt;Xây dựng hoặc Nâng cấp gian hàng này để tăng Độ Nổi Tiếng. Visit gian hàng để trải nghiệm các mini-game và nhận phần thưởng.&lt;/color&gt;</t>
+&lt;color=#737574&gt;Xây dựng hoặc Nâng cấp gian hàng này để tăng Độ Nổi Tiếng. Ghé thăm gian hàng để trải nghiệm các mini-game và nhận phần thưởng.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Một Supply Station dành cho các Tín Đồ sống trong Fabricatorium of the Deep. Butler, người quản lý cửa hàng, đang sắp hết Muối Thánh và sẵn sàng trao đổi.</t>
+          <t>Một Trạm Cung Cấp dành cho các Tín Đồ sống trong Xưởng Dệt của Vực Sâu. Quản gia, người quản lý cửa hàng, đang sắp hết Muối Thánh và sẵn sàng trao đổi.</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Một trong những cơ sở dữ liệu tạp chí tổng hợp yêu cầu cấp độ truy cập cao nhất trên Solaris. Đây là cổng kết nối đến nguồn tài nguyên học thuật của Spacetrek Collective và Startorch Academy. Kho lưu trữ được quản lý bởi Intelligent Retrieval &amp; Indexing Hệ thống, gọi tắt là I.R.I.S.</t>
+          <t>Một trong những cơ sở dữ liệu tạp chí tổng hợp yêu cầu cấp độ truy cập cao nhất trên Solaris. Đây là cổng kết nối đến nguồn tài nguyên học thuật của Spacetrek Collective và Startorch Academy. Kho lưu trữ được quản lý bởi Hệ thống Truy xuất &amp; Lập chỉ mục Thông minh, gọi tắt là I.R.I.S.</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Trung tâm giao thương ngoài trời giữa Startorch Academy và Vương quốc Roya. Vào những khung giờ quy định, thương nhân Roya sẽ mang đến nguyên liệu địa phương và hàng hóa, giúp giảng viên lẫn sinh viên có được đặc sản độc đáo của Lahai-Roi.</t>
+          <t>Trung tâm giao thương ngoài trời giữa Học viện Startorch và Vương quốc Roya. Vào những khung giờ quy định, thương nhân Roya sẽ mang đến nguyên liệu địa phương và hàng hóa, giúp giảng viên lẫn sinh viên có được đặc sản độc đáo của Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Khám phá lại những bảo vật bị lãng quên trên Solaris-3 và trao đổi với Relic Merchant để nhận phần thưởng độc đáo. Search những Rương Nhạc Tâm rải rác khắp thế giới để hồi sinh những kho báu đã mất này.</t>
+          <t>Khám phá lại những bảo vật bị lãng quên trên Solaris-3 và trao đổi với Thương Nhân Di Vật để nhận phần thưởng độc đáo. Tìm kiếm những Rương Nhạc Tâm rải rác khắp thế giới để hồi sinh những kho báu đã mất này.</t>
         </is>
       </c>
     </row>
@@ -9743,7 +9743,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Nền tảng Tổng hợp của Thành phố Ragunna cho phép Resonators dễ dàng chế tạo thuốc, vật liệu xây dựng và tinh luyện các chất.
+          <t>Nền tảng Tổng hợp của Thành phố Ragunna cho phép Resonator dễ dàng chế tạo thuốc, vật liệu xây dựng và tinh luyện các chất.
 Hãy chứng kiến—giờ đây sân khấu thuộc về phản ứng kết hợp.</t>
         </is>
       </c>
@@ -10138,7 +10138,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Gondola Market trôi lững lờ trên những con kênh, chất đầy hoa quả, nguyên liệu, cả bản địa lẫn ngoại nhập. Những chiếc thuyền gondola cập bến với hàng hóa và rời đi với đống Shell Credit chất cao. Mỗi thương vụ thành công, họ lại cất lên những khúc ca ấm áp, vui tươi. Nhưng khi thương vụ thất bại, họ lại khóc than thảm thiết.</t>
+          <t>Chợ Gondola trôi lững lờ trên những con kênh, chất đầy hoa quả, nguyên liệu, cả bản địa lẫn ngoại nhập. Những chiếc thuyền gondola cập bến với hàng hóa và rời đi với đống Shell Credit chất cao. Mỗi thương vụ thành công, họ lại cất lên những khúc ca ấm áp, vui tươi. Nhưng khi thương vụ thất bại, họ lại khóc than thảm thiết.</t>
         </is>
       </c>
     </row>
@@ -10333,7 +10333,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Dodgep mình trong những góc yên tĩnh của Thị trấn Egla là cửa hàng Stillwind Grocery của Vida. Từng là một thương nhân lưu động nổi tiếng khắp Ragunna, giờ Vida sống giản dị nhưng vẫn giữ một danh sách giá đặc biệt cho những khách hàng thân thiết, chứa đầy những bảo vật hiếm có khó tìm...</t>
+          <t>Nép mình trong những góc yên tĩnh của Thị trấn Egla là cửa hàng Stillwind Grocery của Vida. Từng là một thương nhân lưu động nổi tiếng khắp Ragunna, giờ Vida sống giản dị nhưng vẫn giữ một danh sách giá đặc biệt cho những khách hàng thân thiết, chứa đầy những bảo vật hiếm có khó tìm...</t>
         </is>
       </c>
     </row>
@@ -10529,7 +10529,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Chi nhánh Ragunna của Pioneer Association được điều hành bởi Wutherium Film Studio – một bộ phận chuyên về ghi hình tài liệu, nhằm phơi bày cả sự tàn phá lẫn những biến đổi mà thảm họa mang lại.
+          <t>Chi nhánh Ragunna của Hiệp Hội Tiên Phong được điều hành bởi Wutherium Film Studio – một bộ phận chuyên về ghi hình tài liệu, nhằm phơi bày cả sự tàn phá lẫn những biến đổi mà thảm họa mang lại.
 Qua ống kính, Wutherium Film Studio ghi lại những thay đổi bất tận này, khuyến khích nhân loại nhìn nhận lại thế giới xung quanh bằng ánh mắt mới.</t>
         </is>
       </c>
@@ -10595,7 +10595,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Một Tacet Discord Common gặp xuất sắc với tài năng bẩm sinh về giai điệu và nhịp điệu, có thể điều khiển Notepole để biểu diễn bất kỳ bản nhạc nào miễn là có bản nhạc để làm theo.</t>
+          <t>Một Tacet Discord Thường gặp xuất sắc với tài năng bẩm sinh về giai điệu và nhịp điệu, có thể điều khiển Notepole để biểu diễn bất kỳ bản nhạc nào miễn là có bản nhạc để làm theo.</t>
         </is>
       </c>
     </row>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Có báo cáo về việc xuất hiện một Discord hình mãnh thú lớn trên núi Hiên Vân ở Huanglong.
+          <t>Có báo cáo về việc xuất hiện một Tacet Discord hình mãnh thú lớn trên núi Hiên Vân ở Huanglong.
 Theo Hồng Chân Lục: ...Bản tính cô độc, sống một mình... có bốn vuốt và lưng phủ vảy... Dấu chân phát sáng, nên dân địa phương gọi nó là Nghiền Quang.</t>
         </is>
       </c>
@@ -10927,8 +10927,8 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>"Cậu đã nghe chưa? Dưới gốc Cây Wish có một nơi mà những giấc mơ được chắp cánh bay xa. Người ta gọi đó là Lữ Quán Trăng Rằm."
-Khi trăng tròn dần, Jinzhou rộn ràng trong không khí chuẩn bị cho Moon-Chasing Festival. Đây là truyền thống yêu dấu, nơi bạn bè và gia đình quây quần cùng gửi gắm ước nguyện lên bầu trời đêm. Trước khi lễ hội bắt đầu, những lời thì thầm về Lữ Quán Trăng Rằm – nơi ước nguyện thành hiện thực – đã lọt vào tai cậu. Tò mò, cậu quyết định...</t>
+          <t>"Cậu đã nghe chưa? Dưới gốc Cây Ước Nguyện có một nơi mà những giấc mơ được chắp cánh bay xa. Người ta gọi đó là Lữ Quán Trăng Rằm."
+Khi trăng tròn dần, Jinzhou rộn ràng trong không khí chuẩn bị cho Lễ Hội Đuổi Trăng. Đây là truyền thống yêu dấu, nơi bạn bè và gia đình quây quần cùng gửi gắm ước nguyện lên bầu trời đêm. Trước khi lễ hội bắt đầu, những lời thì thầm về Lữ Quán Trăng Rằm – nơi ước nguyện thành hiện thực – đã lọt vào tai cậu. Tò mò, cậu quyết định...</t>
         </is>
       </c>
     </row>
@@ -10993,7 +10993,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Nơi yên tĩnh dưới Tetragon Temple, dành riêng cho các Nữ Tư Tế thiền định và suy ngẫm. Tại đây, trong bóng tối lặng im, họ học cách nhìn vào bên trong, để thấy bằng trái tim và nhận ra chân lý.</t>
+          <t>Nơi yên tĩnh dưới Đền Tetragon, dành riêng cho các Nữ Tư Tế thiền định và suy ngẫm. Tại đây, trong bóng tối lặng im, họ học cách nhìn vào bên trong, để thấy bằng trái tim và nhận ra chân lý.</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Trong Tactical Hologram: Vitreum Dancer, cậu sẽ bị bao vây bởi các đợt Vitreum Dancer. Dodge các đòn tấn công của chúng trong thời gian quy định để hoàn thành thử thách.</t>
+          <t>Trong Tactical Hologram: Vitreum Dancer, cậu sẽ bị bao vây bởi các đợt Vitreum Dancer. Né tránh các đòn tấn công của chúng trong thời gian quy định để hoàn thành thử thách.</t>
         </is>
       </c>
     </row>
@@ -11323,8 +11323,8 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Cartethyia đã truyền vào Gravity Calibrator một nguồn năng lượng đặc biệt. 
-Hãy dùng Gravity Calibrator để &lt;color=#ffd12f&gt;thay đổi hướng trọng lực&lt;/color&gt;, mở ra những khu vực không thể tiếp cận trước đây.</t>
+          <t>Cartethyia đã truyền vào Bộ Điều Chỉnh Trọng Lực một nguồn năng lượng đặc biệt. 
+Hãy dùng Bộ Điều Chỉnh Trọng Lực để &lt;color=#ffd12f&gt;thay đổi hướng trọng lực&lt;/color&gt;, mở ra những khu vực không thể tiếp cận trước đây.</t>
         </is>
       </c>
     </row>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Board the Gondola và đi theo ánh sáng để đến đích.
+          <t>Lên thuyền gondola và đi theo ánh sáng để đến đích.
 Bay qua &lt;color=#ffd12f&gt;Vòng Tăng Tốc&lt;/color&gt; để duy trì tốc độ và tránh &lt;color=#ffd12f&gt;Vòng Cản Trở&lt;/color&gt; trên đường đi.</t>
         </is>
       </c>
@@ -11590,7 +11590,7 @@
       <c r="M167" t="inlineStr">
         <is>
           <t>"Bờ bến của gặp gỡ, hiểu biết và khát khao."
-Second Coming of Solaris đã tái tạo lại một ký ức quan trọng. Hãy đến &lt;color=HighlightB&gt;Cube Người Gác Bờ&lt;/color&gt; để hoàn thành bộ sưu tập Ký Ức Du Hành."</t>
+Sự Trở Lại Của Solaris đã tái tạo lại một ký ức quan trọng. Hãy đến &lt;color=HighlightB&gt;Khối Lập Phương Người Gác Bờ&lt;/color&gt; để hoàn thành bộ sưu tập Ký Ức Du Hành."</t>
         </is>
       </c>
     </row>
@@ -11657,7 +11657,7 @@
       <c r="M168" t="inlineStr">
         <is>
           <t>"Bình minh chúng ta cùng ngắm. Ấm áp làm sao."
-Second Coming of Solaris đã tái tạo lại một ký ức quan trọng. Hãy đến &lt;color=HighlightB&gt;KU-Lolo&lt;/color&gt; để hoàn thành bộ sưu tập Ký Ức Du Hành."</t>
+Sự Trở Lại Của Solaris đã tái tạo lại một ký ức quan trọng. Hãy đến &lt;color=HighlightB&gt;KU-Lolo&lt;/color&gt; để hoàn thành bộ sưu tập Ký Ức Du Hành."</t>
         </is>
       </c>
     </row>
@@ -11724,7 +11724,7 @@
       <c r="M169" t="inlineStr">
         <is>
           <t>Cô ấy mời Nhà Thơ lên sân khấu.
-Second Coming of Solaris đã tái tạo lại một ký ức quan trọng. Hãy đến &lt;color=HighlightB&gt;KU-Lolo&lt;/color&gt; để hoàn thành bộ sưu tập Du Hành Ký Ức.</t>
+Sự Trở Lại Của Solaris đã tái tạo lại một ký ức quan trọng. Hãy đến &lt;color=HighlightB&gt;KU-Lolo&lt;/color&gt; để hoàn thành bộ sưu tập Du Hành Ký Ức.</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       <c r="M171" t="inlineStr">
         <is>
           <t>"Nhờ có cậu, những đêm mưa ở Ragunna giờ có ý nghĩa mới.
-Second Coming of Solaris đã tái tạo lại một ký ức quan trọng. Hãy đến &lt;color=HighlightB&gt;Carlotta Cube&lt;/color&gt; để hoàn thành bộ sưu tập Ký Ức Du Hành."</t>
+Sự Trở Lại Của Solaris đã tái tạo lại một ký ức quan trọng. Hãy đến &lt;color=HighlightB&gt;Carlotta Cube&lt;/color&gt; để hoàn thành bộ sưu tập Ký Ức Du Hành."</t>
         </is>
       </c>
     </row>
@@ -12059,7 +12059,7 @@
       <c r="M174" t="inlineStr">
         <is>
           <t>"Một cuộc phiêu lưu nhỏ được cất giấu trong Kho Tàng."
-Second Coming of Solaris đã tái tạo lại một ký ức quan trọng. Hãy đến &lt;color=HighlightB&gt;KU-Lolo&lt;/color&gt; để hoàn thành bộ sưu tập Du Hành Ký Ức.</t>
+Sự Trở Lại Của Solaris đã tái tạo lại một ký ức quan trọng. Hãy đến &lt;color=HighlightB&gt;KU-Lolo&lt;/color&gt; để hoàn thành bộ sưu tập Du Hành Ký Ức.</t>
         </is>
       </c>
     </row>
@@ -12193,7 +12193,7 @@
       <c r="M176" t="inlineStr">
         <is>
           <t>"Dù trong bóng tối không chút ánh trăng, nanh vuốt vẫn luôn thao thức."
-Second Coming of Solaris đã tái tạo một ký ức quan trọng. Hãy đến &lt;color=HighlightB&gt;Calcharo Cube&lt;/color&gt; để hoàn tất bộ sưu tập Du Hành Ký Ức.</t>
+Sự Trở Lại Của Solaris đã tái tạo một ký ức quan trọng. Hãy đến &lt;color=HighlightB&gt;Khối Calcharo&lt;/color&gt; để hoàn tất bộ sưu tập Du Hành Ký Ức.</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Averardo Bank đã mở rộng mạng lưới quầy giao dịch khắp Septimont, nhằm mở rộng hoạt động trong thành phố sầm uất này. Clerk Raechyl đang đảm nhiệm công việc khôi phục Monnaie, và khối lượng công việc đang chồng chất.</t>
+          <t>Ngân Hàng Averardo đã mở rộng mạng lưới quầy giao dịch khắp Septimont, nhằm mở rộng hoạt động trong thành phố sầm uất này. Nhân viên Raechyl đang đảm nhiệm công việc khôi phục Monnaie, và khối lượng công việc đang chồng chất.</t>
         </is>
       </c>
     </row>
@@ -12388,7 +12388,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Một cánh cổng bí ẩn xuất hiện tại Bãi Lầy Aix Rên Rỉ, mở ra một thế giới gọi là Somnoire. Tương truyền, nơi đây chứa đựng những giấc mơ của tất cả sinh linh ở Solaris.</t>
+          <t>Một cánh cổng bí ẩn hiện ra tại Đầm Than Vãn Aix, mở lối đến cõi Somnoire. Theo truyền thuyết, nơi đây chứa đựng giấc mơ của mọi sinh linh trên Solaris.</t>
         </is>
       </c>
     </row>
@@ -12454,8 +12454,8 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Discord Độc Nhất. Một Gulpuff sinh ra từ dữ liệu dị thường, sinh vật này sở hữu kích thước khổng lồ và sức hủy diệt đáng sợ.
-Dù Gulpuff thường là Discord hạng Phổ Thông, con này đã đạt được khả năng chiến đấu vượt trội và tính khí hung dữ do ảnh hưởng của dữ liệu dị thường. Khuyến cáo nên giữ khoảng cách an toàn.</t>
+          <t>Tacet Discord Độc Nhất. Một Gulpuff sinh ra từ dữ liệu dị thường, sinh vật này sở hữu kích thước khổng lồ và sức hủy diệt đáng sợ.
+Dù Gulpuff thường là Tacet Discord hạng Phổ Thông, con này đã đạt được khả năng chiến đấu vượt trội và tính khí hung dữ do ảnh hưởng của dữ liệu dị thường. Khuyến cáo nên giữ khoảng cách an toàn.</t>
         </is>
       </c>
     </row>
@@ -12522,7 +12522,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Discord Độc Nhất. Một Fusion Warrior sinh ra từ dữ liệu dị thường, sở hữu kỹ năng chiến đấu vượt xa trí tưởng tượng.
+          <t>Tacet Discord Độc Nhất. Một Chiến Binh Fusion sinh ra từ dữ liệu dị thường, sở hữu kỹ năng chiến đấu vượt xa trí tưởng tượng.
 Hai lưỡi kiếm thay thế đôi tay của hắn gần như có tri giác riêng, khai thác mọi sơ hở trong tư thế của đối thủ.
 Tần số cụ thể mà hắn bắt chước để đạt đến trình độ kiếm thuật như vậy vẫn còn là một bí ẩn.</t>
         </is>
@@ -12591,7 +12591,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Echo Độc Nhất. Một đàn Cruisewing tụ tập do dữ liệu dị thường, thể hiện mức độ phối hợp nhất định.
+          <t>Tổ Tacet Độc Nhất. Một đàn Cruisewing tụ tập do dữ liệu dị thường, thể hiện mức độ phối hợp nhất định.
 Dù từng cá thể Cruisewing yếu ớt, sức mạnh tập thể của chúng có thể tạo nên một cơn bão khủng khiếp.
 Đừng bao giờ đánh giá thấp sức chiến đấu của đàn này.</t>
         </is>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Discord Độc Nhất. Một Rocksteady Guardian hình thành từ dữ liệu dị thường, có thể đập vỡ nhiều lớp đá chỉ bằng một cú đánh.
+          <t>Tacet Discord Độc Nhất. Một Rocksteady Guardian hình thành từ dữ liệu dị thường, có thể đập vỡ nhiều lớp đá chỉ bằng một cú đánh.
 Dù di chuyển chậm chạp, sức mạnh hủy diệt của nó hoàn toàn bù đắp cho nhược điểm đó.
 Sức mạnh thô bạo, đơn giản mà hiệu quả.</t>
         </is>
@@ -13130,7 +13130,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Một Echo tại khu vực Fagaceae Peninsula. Hoàn thành thử thách để nhận Mẫu Giấc Mơ và phần thưởng.
+          <t>Một Tổ Tacet tại khu vực Bán Đảo Fagaceae. Hoàn thành thử thách để nhận Mẫu Giấc Mơ và phần thưởng.
 "Hãy để ta gục ngã trong bão tố. Nguyện vinh quang của Sentinel trường tồn mãi mãi."</t>
         </is>
       </c>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Một Echo tại khu vực Fagaceae Peninsula. Thử thách đã hoàn thành và có thể thách đấu lại.
+          <t>Một Tổ Tacet tại khu vực Bán Đảo Fagaceae. Thử thách đã hoàn thành và có thể thách đấu lại.
 "Hãy để ta gục ngã trong bão tố. Nguyện vinh quang của Sentinel trường tồn mãi mãi."</t>
         </is>
       </c>
@@ -13264,7 +13264,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Một Echo tại khu vực Fagaceae Peninsula. Hoàn thành thử thách để nhận Mẫu Giấc Mơ và phần thưởng.
+          <t>Một Tổ Tacet tại khu vực Bán Đảo Fagaceae. Hoàn thành thử thách để nhận Mẫu Giấc Mơ và phần thưởng.
 "Mấy chục năm nữa, ta tin Rinascita sẽ thịnh vượng như một quốc gia tự do và đoàn kết. Cậu không nghĩ vậy sao?"</t>
         </is>
       </c>
@@ -13331,7 +13331,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Một Echo tại khu vực Fagaceae Peninsula. Thử thách đã hoàn thành và có thể thách đấu lại.
+          <t>Một Tổ Tacet tại khu vực Bán Đảo Fagaceae. Thử thách đã hoàn thành và có thể thách đấu lại.
 "Mấy chục năm nữa, ta tin Rinascita sẽ thịnh vượng như một quốc gia tự do và đoàn kết. Cậu không nghĩ vậy sao?"</t>
         </is>
       </c>
@@ -15006,7 +15006,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Một Nút Giấc Mơ tại Zargon Garden: Ruins. Hoàn thành thử thách để nhận Mẫu Giấc Mơ và phần thưởng.
+          <t>Một Nút Giấc Mơ tại Vườn Zargon: Tàn Tích. Hoàn thành thử thách để nhận Mẫu Giấc Mơ và phần thưởng.
 "Và trong cõi mộng, ngươi tìm lại được thời huy hoàng."</t>
         </is>
       </c>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Một Nút Giấc Mơ tại Zargon Garden: Ruins. Thử thách này đã hoàn thành và có thể thách đấu lại.
+          <t>Một Nút Giấc Mơ tại Vườn Zargon: Tàn Tích. Thử thách này đã hoàn thành và có thể thách đấu lại.
 "Và trong cõi mộng, ngươi tìm lại được thời huy hoàng."</t>
         </is>
       </c>
@@ -15271,7 +15271,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Một Nút Mộng Ảnh ở Titanbone Expanse. Hoàn thành thử thách để nhận Mẫu Giấc Mơ và phần thưởng. "Mấy người dám thách đấu cả ba chúng ta à? Nhưng liệu sức mạnh có xứng với lòng dũng cảm không?"</t>
+          <t>Một Nút Mộng Ảnh ở Titanbone Expanse. Hoàn thành thử thách để nhận Mẫu Giấc Mơ và phần thưởng. "Mấy người dám thách đấu cả ba chúng tao à? Nhưng liệu sức mạnh có xứng với lòng dũng cảm không?"</t>
         </is>
       </c>
     </row>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Một Echo tại Dãy Border Mountains. Hoàn thành thử thách để nhận Mẫu Giấc Mơ và phần thưởng. "Hãy chiêm ngưỡng dòng chảy Tàn Dư của sự hủy diệt! Vĩ đại nhất! Bất khả chiến bại! Vô đối!"</t>
+          <t>Một Tổ Tacet tại Dãy Núi Biên Giới. Hoàn thành thử thách để nhận Mẫu Giấc Mơ và phần thưởng. "Hãy chiêm ngưỡng dòng chảy Tàn Dư của sự hủy diệt! Vĩ đại nhất! Bất khả chiến bại! Vô đối!"</t>
         </is>
       </c>
     </row>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Trong Tactical Hologram: Vitreum Dancer, cậu sẽ bị bao vây bởi các đợt Vitreum Dancer. Dodge các đòn tấn công của chúng trong thời gian quy định để hoàn thành thử thách.</t>
+          <t>Trong Tactical Hologram: Vitreum Dancer, cậu sẽ bị bao vây bởi các đợt Vitreum Dancer. Né tránh các đòn tấn công của chúng trong thời gian quy định để hoàn thành thử thách.</t>
         </is>
       </c>
     </row>
@@ -16195,7 +16195,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Trong Tactical Hologram: Vitreum Dancer, cậu sẽ bị bao vây bởi các đợt Vitreum Dancer. Dodge các đòn tấn công của chúng trong thời gian quy định để hoàn thành thử thách.</t>
+          <t>Trong Tactical Hologram: Vitreum Dancer, cậu sẽ bị bao vây bởi các đợt Vitreum Dancer. Né tránh các đòn tấn công của chúng trong thời gian quy định để hoàn thành thử thách.</t>
         </is>
       </c>
     </row>
@@ -16260,7 +16260,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Trong Tactical Hologram: Vitreum Dancer, cậu sẽ bị bao vây bởi các đợt Vitreum Dancer. Dodge các đòn tấn công của chúng trong thời gian quy định để hoàn thành thử thách.</t>
+          <t>Trong Tactical Hologram: Vitreum Dancer, cậu sẽ bị bao vây bởi các đợt Vitreum Dancer. Né tránh các đòn tấn công của chúng trong thời gian quy định để hoàn thành thử thách.</t>
         </is>
       </c>
     </row>
@@ -16726,7 +16726,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Những người qua đường thường bị thu hút bởi đôi bàn tay thanh thoát vươn ra từ Averardo Bank. Đôi tay ấy được chăm chút hoàn hảo, luôn cử động với vẻ duyên dáng và thanh lịch...
+          <t>Những người qua đường thường bị thu hút bởi đôi bàn tay thanh thoát vươn ra từ Ngân Hàng Averardo. Đôi tay ấy được chăm chút hoàn hảo, luôn cử động với vẻ duyên dáng và thanh lịch...
 Dù chủ nhân chỉ là một nhân viên giao dịch Echo.</t>
         </is>
       </c>
@@ -16792,7 +16792,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Từng là một tiếng vọng cô đơn trôi dạt trên biển cả, Lario đã trải qua nhiều năm tháng không bạn đồng hành cho đến khi gia nhập Đoàn Kẻ Ngốc. Mọi người chỉ biết đến giống loài của nó—Pliosaurus Somnii. Dù đoàn đã đi qua biết bao vùng biển gần Rinascita, họ vẫn chưa từng gặp một cá thể nào giống nó.</t>
+          <t>Từng là một Echo cô đơn trôi dạt trên biển cả, Lario đã trải qua nhiều năm tháng không bạn đồng hành cho đến khi gia nhập Đoàn Kẻ Ngốc. Mọi người chỉ biết đến giống loài của nó—Pliosaurus Somnii. Dù đoàn đã đi qua biết bao vùng biển gần Rinascita, họ vẫn chưa từng gặp một cá thể nào giống nó.</t>
         </is>
       </c>
     </row>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Xưa kia, khi Hắc Triều tàn phá thành phố và Tacet Field lan tràn như dịch bệnh, nhiệm vụ của Bạch Tuộc Quý Ông là thổi còi báo động. Những ngày ấy giờ chỉ như giấc mơ xa xăm, thế mà ông vẫn đều đặn thổi kèn báo giờ, âm thầm bảo vệ sự bình yên cho thành phố.</t>
+          <t>Xưa kia, khi Hắc Triều tàn phá thành phố và Tổ Tacet lan tràn như dịch bệnh, nhiệm vụ của Bạch Tuộc Quý Ông là thổi còi báo động. Những ngày ấy giờ chỉ như giấc mơ xa xăm, thế mà ông vẫn đều đặn thổi kèn báo giờ, âm thầm bảo vệ sự bình yên cho thành phố.</t>
         </is>
       </c>
     </row>
@@ -17052,7 +17052,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Ban đầu được biến đổi từ những con búp bê bỏ đi, những Echoes bông này đã tiến hóa đến mức có thể cảm nhận những cảm xúc tinh tế của con người. Với chúng, những cảm xúc ấy chính là những tần số ngon lành để thưởng thức một cách say mê.</t>
+          <t>Ban đầu được biến đổi từ những con búp bê bỏ đi, những Echo bông này đã tiến hóa đến mức có thể cảm nhận những cảm xúc tinh tế của con người. Với chúng, những cảm xúc ấy chính là những tần số ngon lành để thưởng thức một cách say mê.</t>
         </is>
       </c>
     </row>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Xuất hiện khắp các con phố ở Ragunna, Tubpups là những Echoes sôi động, luôn đồng hành như những người bạn trung thành. Dù chơi đùa cùng trẻ nhỏ, mang vác dụng cụ nghệ thuật, hay làm giỏ đựng đồ tiện lợi, chúng luôn mang đến niềm vui và năng lượng ở mọi nơi.</t>
+          <t>Xuất hiện khắp các con phố ở Ragunna, Tubpups là những Echo sôi động, luôn đồng hành như những người bạn trung thành. Dù chơi đùa cùng trẻ nhỏ, mang vác dụng cụ nghệ thuật, hay làm giỏ đựng đồ tiện lợi, chúng luôn mang đến niềm vui và năng lượng ở mọi nơi.</t>
         </is>
       </c>
     </row>
@@ -17183,7 +17183,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Mist dâng lên trên biển, mang theo những âm thanh vọng lại từ khắp nơi—tiếng hát, tiếng cối xay gió kẽo kẹt, và tiếng ồn ào náo nhiệt của phố phường. Với những thủy thủ đã mệt mỏi vì cuộc sống đơn điệu trên biển, những âm thanh ấy trở thành lời mời gọi không thể cưỡng lại. Mê hoặc, họ lái thuyền tiến thẳng vào lòng sương mù, không hề hay biết mình đang lao vào bẫy của Discord...
+          <t>Sương mù dâng lên trên biển, mang theo những âm thanh vọng lại từ khắp nơi—tiếng hát, tiếng cối xay gió kẽo kẹt, và tiếng ồn ào náo nhiệt của phố phường. Với những thủy thủ đã mệt mỏi vì cuộc sống đơn điệu trên biển, những âm thanh ấy trở thành lời mời gọi không thể cưỡng lại. Mê hoặc, họ lái thuyền tiến thẳng vào lòng sương mù, không hề hay biết mình đang lao vào bẫy của Tacet Discord...
 Nhưng như mọi câu chuyện nơi tuyệt vọng ngự trị, một tia hy vọng ắt sẽ xuất hiện. Ngay cả trong vùng biển nguy hiểm này, vẫn sẽ có người phá tan bão tố, mang ánh sáng đến cho tất cả.</t>
         </is>
       </c>
@@ -17249,7 +17249,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Nơi ở của Fish King bí ẩn, như được chỉ ra trên bản đồ kho báu. Loài cá cực kỳ hiếm này dường như sở hữu một sức mạnh vượt xa các sinh vật thủy sinh thông thường.</t>
+          <t>Nơi ở của Vua Cá bí ẩn, như được chỉ ra trên bản đồ kho báu. Loài cá cực kỳ hiếm này dường như sở hữu một sức mạnh vượt xa các sinh vật thủy sinh thông thường.</t>
         </is>
       </c>
     </row>
@@ -17314,7 +17314,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Dù Threnodian đã biến mất, bóng tối của nó vẫn còn vương vấn. Hãy giúp Spacetrek Collective tiêu diệt những mối đe dọa không ngừng trên Dimmr Plains. Có vẻ như những lưỡi kiếm băng tìm thấy trên đồng bằng có thể được sử dụng như công cụ mạnh mẽ...</t>
+          <t>Dù Threnodian đã biến mất, bóng tối của nó vẫn còn vương vấn. Hãy giúp Tập Đoàn Spacetrek tiêu diệt những mối đe dọa không ngừng trên Đồng Bằng Dimmr. Có vẻ như những lưỡi kiếm băng tìm thấy trên đồng bằng có thể được sử dụng như công cụ mạnh mẽ...</t>
         </is>
       </c>
     </row>
@@ -17715,7 +17715,7 @@
 Lũ trẻ đang khóc. Tiếng nức nở của chúng bị nuốt chửng trong tiếng gầm của Kerasaur. Thea đã đúng… Con quái vật đó đang lao thẳng về phía chúng ta. Chắc nó đã phát hiện ra ████.
 Chúng ta vẫn có thể chạy. Vẫn còn đủ sức để thoát thân. Nhưng bọn trẻ thì sao? Chúng thậm chí không vượt qua nổi chiến hào. Một khi bức tường sụp đổ, không còn nghi ngờ gì về số phận của chúng.
 …Chúng ta từng là đồ vô lại. Bán linh hồn để kiếm tiền. Nhưng rồi cũng chuộc lại được. ██ thật thú vị. Ai ngờ được? Lũ tội phạm già như chúng ta, ██ suốt mấy chục năm, giờ lại cầm vũ khí bảo vệ Septimont.
-Lưng Myzel còng hơn cả thanh kiếm hắn đang nắm chặt. Cây giáo của Beccan—vật đã theo hắn qua hàng chục trận chiến—giờ chỉ còn là cây gậy chống. Ta cũng chẳng khá hơn. Mắt mờ, không biết còn bắn trúng mục tiêu như hồi còn là ██ không. Chúng ta đều từng là ████. Thời gian thật không tha thứ.
+Lưng Myzel còng hơn cả thanh kiếm hắn đang nắm chặt. Cây giáo của Beccan—vật đã theo hắn qua hàng chục trận chiến—giờ chỉ còn là cây gậy chống. Tao cũng chẳng khá hơn. Mắt mờ, không biết còn bắn trúng mục tiêu như hồi còn là ██ không. Chúng ta đều từng là ████. Thời gian thật không tha thứ.
 Trước khi rời đi, chúng ta chọn một đứa lớn hơn đi cùng. Nếu chúng ta ████ ở đó, nó phải sống sót mà về. Báo động. Cho những đứa khác cơ hội chạy trốn.
 ██ đã gần rồi. Thôi thì, những kẻ thù cũ của ta… đã đến lúc. Đến lúc gặp ██ trên chiến trường.
 Ta chúc ngươi, ta, và tất cả mọi người… săn bắn vui vẻ."</t>
@@ -17793,13 +17793,13 @@
       <c r="M260" t="inlineStr">
         <is>
           <t>((Dòng chữ bị cố tình xóa mờ đi.)
-"Damn it… Ta đã bảo không nên để bọn trẻ đối mặt với Mây Độc. Giờ chỉ còn lại lũ ████ vô dụng này. Làm sao chúng ta ngăn được bọn Kerasaur chứ?"
+"Chết tiệt… Tao đã bảo không nên để bọn trẻ đối mặt với Mây Độc. Giờ chỉ còn lại lũ ████ vô dụng này. Làm sao chúng ta ngăn được bọn Kerasaur chứ?"
 "Thì có sao. Nếu không thiếu người, tụi mình vẫn đang thối rữa trong ██ thôi."
 "Chúng ta đã sống đủ rồi. Chết ở đây cũng chẳng hối tiếc. Nhưng bọn trẻ… chúng là tương lai của Septimont. Chúng xứng đáng được lớn lên."
 "Đừng có mà diễn thuyết. Thực tế thì làm gì bây giờ? Cố đưa chúng đi? Với ██ đang bao vây, chẳng còn nơi nào an toàn hơn đây cả."
-"Vậy thì giải quyết theo cách của ████. Lâu lắm rồi không cầm vũ khí. Ngươi chưa quên cách chiến đấu chứ, hả?"
-"Hừ. Đừng có coi thường ta! Ta mà xiên chết mấy con Kerasaur xong, sẽ cho ngươi nếm thử giáo của ta luôn!"
-"Giáo gì của ngươi? Cả nói chuyện còn thở hổn hển, lão già khốn kiếp!"
+"Vậy thì giải quyết theo cách của ████. Lâu lắm rồi không cầm vũ khí. Mày chưa quên cách chiến đấu chứ, hả?"
+"Hừ. Đừng có coi thường tao! Tao mà xiên chết mấy con Kerasaur xong, sẽ cho mày nếm thử giáo của tao luôn!"
+"Giáo gì của mày? Cả nói chuyện còn thở hổn hển, lão già khốn kiếp!"
 "Tch… im đi. Còn thở là còn đánh. Và còn đánh là bọn chúng chưa thắng."
 "Đúng thế. Nếu đã phải ngã xuống… Lần tới khi người ta nhắc đến chúng ta, có lẽ họ sẽ gọi ta bằng cái tên khác, không phải ████..."</t>
         </is>
@@ -18057,7 +18057,7 @@
 Trái Tim Sói Cô Đơn:
 Chuẩn luôn! Trận chiến đó thật điên rồ!
 Người Bán Đồ AAA:
-Ready thắp sáng đấu trường chưa? Ghé Mars Industry nào! Trang bị đầy đủ và tiến tới vinh quang!
+Sẵn sàng thắp sáng đấu trường chưa? Ghé Mars Industry nào! Trang bị đầy đủ và tiến tới vinh quang!
 Móng Vuốt Sắc:
 Đủ rồi mấy cái quảng cáo sến súa! Đi lấy cờ đi! Cờ phấp phới, chiến thắng gọi tên!
 ...</t>
@@ -18349,7 +18349,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Centuries ago, một đấu sĩ cô độc cùng người hầu của mình canh giữ một tháp canh ven biển, xa rời đấu trường và ẩn sâu trong vùng hoang dã. Giờ đây, tòa tháp mang đầy vết tích của Bóng Tối Tràn Đến—phong sương mòn mỏi, nứt nẻ nhưng vẫn đứng vững, như một tấm bia mộ cho câu chuyện bị lãng quên.
+          <t>Cách đây hàng thế kỷ, một đấu sĩ cô độc cùng người hầu của mình canh giữ một tháp canh ven biển, xa rời đấu trường và ẩn sâu trong vùng hoang dã. Giờ đây, tòa tháp mang đầy vết tích của Bóng Tối Tràn Đến—phong sương mòn mỏi, nứt nẻ nhưng vẫn đứng vững, như một tấm bia mộ cho câu chuyện bị lãng quên.
 Gần đây, một nhà sinh thái học trẻ tuổi đã xuất hiện gần tháp, bị thu hút bởi tiếng gầm quen thuộc vọng ra từ bên trong...</t>
         </is>
       </c>
@@ -18622,7 +18622,7 @@
         <is>
           <t>Những cảm xúc và nhịp điệu mãnh liệt sẽ tác động đến biển sâu và Vùng Ngoài, nhấn chìm mọi sinh linh vào cơn hỗn loạn không thể kiểm soát.
 Được rồi, được rồi...
-Calm nào, suy nghĩ kỹ đi: Loại âm nhạc nào mới có sức mạnh dẫn dắt và xoa dịu vạn vật?</t>
+Bình tĩnh nào, suy nghĩ kỹ đi: Loại âm nhạc nào mới có sức mạnh dẫn dắt và xoa dịu vạn vật?</t>
         </is>
       </c>
     </row>
@@ -18690,7 +18690,7 @@
       <c r="M272" t="inlineStr">
         <is>
           <t>Họ luôn dõi theo khi ta Điều Khiển những giai điệu, như thể muốn thấu hiểu bí ẩn của chúng.
-Họ mong chiếm đoạt sức mạnh này, mà không biết rằng những khúc ca vang bên tai họ chính là lời thì thầm của cái chết – thứ họ cố gắng tránh Dodge.
+Họ mong chiếm đoạt sức mạnh này, mà không biết rằng những khúc ca vang bên tai họ chính là lời thì thầm của cái chết – thứ họ cố gắng tránh né.
 Nếu họ đòi hỏi, ép buộc, liệu ta có trao cho họ điều họ muốn? Liệu họ có chấp nhận?</t>
         </is>
       </c>
@@ -18891,7 +18891,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Lồng ấp Echo Vi mô được lưu trữ tập trung và chiếm không gian đáng kể. Để tiết kiệm diện tích sàn sản xuất quý giá, chúng thường được giấu trong các vách cấu trúc.
+          <t>Lồng ấp Tiếng Vọng Vi mô được lưu trữ tập trung và chiếm không gian đáng kể. Để tiết kiệm diện tích sàn sản xuất quý giá, chúng thường được giấu trong các vách cấu trúc.
 Các đơn vị này triển khai nhanh chóng khi kích hoạt. Nhân viên được khuyến cáo phải hết sức thận trọng và luôn cảnh giác tình hình để tránh thương tích.</t>
         </is>
       </c>
@@ -18959,7 +18959,7 @@
       <c r="M276" t="inlineStr">
         <is>
           <t>Vox Santus chịu trách nhiệm thu thập và phát lại các đoạn giai điệu trong khu vực được chỉ định. Những giai điệu này sẽ được phát lại liên tục khi cần thiết. Trong trường hợp thiết bị gặp trục trặc, hãy thử hiệu chỉnh lại qua Vox Santus trước.
-Warning: Nghiêm cấm sử dụng trong các sự kiện hỏng hóc Fabricatorium. Những giai điệu méo mó có thể gây ra tác động ngoài ý muốn đối với cá nhân.</t>
+Cảnh báo: Nghiêm cấm sử dụng trong các sự kiện hỏng hóc Fabricatorium. Những giai điệu méo mó có thể gây ra tác động ngoài ý muốn đối với cá nhân.</t>
         </is>
       </c>
     </row>
@@ -19049,9 +19049,9 @@
 Clement, vị Primus duy nhất xuất thân từ dòng họ Fisalia, đã dẫn dắt việc chính thức hệ thống hóa các giáo lý của Order với sự hỗ trợ của gia tộc Fisalia. Được hậu thuẫn bởi tài sản khổng lồ của gia đình, ông đã nâng tầm ảnh hưởng và sức mạnh của Order lên một tầm cao mới. Tuy nhiên, sự ổn định tinh thần của ông dần suy giảm trong những năm cuối đời, dẫn đến những nỗ lực bất thường nhằm thay đổi các giáo lý cơ bản—cho đến khi ông qua đời đột ngột.
 Chính sử ghi nhận cái chết của ông là do các nghi lễ bí mật của gia tộc Fisalia. Thế nhưng, liệu tâm trí rạn nứt của ông là hậu quả của những nghi lễ đó hay do ảnh hưởng của thế lực đen tối nào khác vẫn là một chủ đề thảo luận hấp dẫn.
 Primus Kỹ Trị, Vester Đệ Nhất
-Một nhà tiên phong đặt niềm tin lớn vào tiến bộ khoa học, Primus Vester Đệ Nhất đã dẫn đầu sự phát triển không ngừng của công nghệ Common Echoes.
-Thành tựu vĩ đại nhất của ông là việc tinh chỉnh kỹ thuật chỉnh sửa tần số, giúp rút ngắn thời gian cần thiết để kết nối các tần số dư thừa của Tacet Discord và củng cố quyền kiểm soát của Order đối với công nghệ tổng hợp tần số tầm xa. Lần đầu tiên, tất cả các Common Echoes do Order vận hành trong Rinascita có thể duy trì trạng thái tổng hợp tần số vĩnh viễn.
-Thành tựu này khiến việc thu hồi và phá hủy Echoes định kỳ trở nên lỗi thời, trừ những trường hợp đặc biệt. Đây là một bước nhảy vọt trong việc vượt qua các ràng buộc không thời gian đối với Common Echoes và tăng cường đáng kể sự ổn định của chúng.
+Một nhà tiên phong đặt niềm tin lớn vào tiến bộ khoa học, Primus Vester Đệ Nhất đã dẫn đầu sự phát triển không ngừng của công nghệ Common Echo.
+Thành tựu vĩ đại nhất của ông là việc tinh chỉnh kỹ thuật chỉnh sửa tần số, giúp rút ngắn thời gian cần thiết để kết nối các tần số dư thừa của Tacet Discord và củng cố quyền kiểm soát của Order đối với công nghệ tổng hợp tần số tầm xa. Lần đầu tiên, tất cả các Common Echo do Order vận hành trong Rinascita có thể duy trì trạng thái tổng hợp tần số vĩnh viễn.
+Thành tựu này khiến việc thu hồi và phá hủy Echo định kỳ trở nên lỗi thời, trừ những trường hợp đặc biệt. Đây là một bước nhảy vọt trong việc vượt qua các ràng buộc không thời gian đối với Common Echo và tăng cường đáng kể sự ổn định của chúng.
 Primus Lễ Hội, Pettini
 Một nhà cai trị cởi mở và khoan dung phi thường, Pettini đã mở ra một kỷ nguyên thịnh vượng chưa từng có. Xã hội phát triển rực rỡ, đánh dấu bởi những tiến bộ vượt bậc trong công nghệ và triết học. Thế nhưng, khi những ràng buộc truyền thống dần sụp đổ, con người trở nên phóng túng. Niềm tin của họ bị xói mòn, họ bắt đầu đặt câu hỏi về Thần Tính. Điều khởi đầu như một sự khai sáng đã biến thành bất đồng.
 Vì vậy, Pettini trở thành kiến trúc sư của sự suy tàn trong hoan lạc. Theo thời gian, những nhà cải cách nổi dậy phản đối và tước đi Ngai Primus của ông.
@@ -19130,8 +19130,8 @@
           <t>Hai gia tộc lớn đã chia rẽ về vấn đề liệu có nên thiết lập một tín ngưỡng chính thức cho Sentinel hay không.
 Gia tộc Fisalias cho rằng Rinascita không được lặp lại số phận của những quần đảo đã sụp đổ và không thể tiếp tục chịu đựng sự cai trị phân mảnh. Họ ủng hộ việc xây dựng một tín ngưỡng thống nhất để dẫn dắt dân chúng, với Sentinel là vị thần tối cao. Theo quan điểm của họ, việc thiết lập tín ngưỡng này cũng là cách Rinascita bày tỏ lòng biết ơn đối với Sentinel.
 Ngược lại hoàn toàn, các chiến binh Abrogati lại cho rằng Sentinel là một phép màu hiếm có và không thể tái hiện theo ý muốn. Họ lập luận rằng đặt hy vọng vào một vị thần có sự hiện diện không chắc chắn là điều ngu ngốc và hèn nhát. Sentinel đã thể hiện lòng nhân từ vô bờ khi dẫn dắt người dân Rinascita đến vùng đất mới. Việc tiếp tục cầu nguyện để được can thiệp thêm là không phù hợp. Thay vào đó, họ khẳng định con người phải nỗ lực trở thành những chiến binh xứng đáng đứng bên cạnh một vị thần như vậy, đối mặt với tai họa không phải bằng cầu xin, mà bằng sức mạnh.
-Sự khác biệt giữa hai thế lực, vốn đã chất chứa căng thẳng lịch sử, cuối cùng đã bùng phát thành xung đột quy mô lớn. Chỉ khi Discord tấn công Rinascita, cả hai bên mới nhận ra vùng đất mới này còn lâu mới là nơi họ có thể an tâm nghỉ ngơi.
-Sau cuộc khủng hoảng Discord và sau những cuộc đàm phán kéo dài, phe Abrogati cùng những người ủng hộ đã di chuyển về phía tây vào vùng hoang dã, nơi họ thành lập Septimont. Trong khi đó, gia tộc Fisalias dẫn dắt những người ở lại xây dựng nên Ragunna.</t>
+Sự khác biệt giữa hai thế lực, vốn đã chất chứa căng thẳng lịch sử, cuối cùng đã bùng phát thành xung đột quy mô lớn. Chỉ khi Tacet Discord tấn công Rinascita, cả hai bên mới nhận ra vùng đất mới này còn lâu mới là nơi họ có thể an tâm nghỉ ngơi.
+Sau cuộc khủng hoảng Tacet Discord và sau những cuộc đàm phán kéo dài, phe Abrogati cùng những người ủng hộ đã di chuyển về phía tây vào vùng hoang dã, nơi họ thành lập Septimont. Trong khi đó, gia tộc Fisalias dẫn dắt những người ở lại xây dựng nên Ragunna.</t>
         </is>
       </c>
     </row>
@@ -19561,8 +19561,8 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Sản lượng Echoes ở Anima Cradle đã tăng gấp đôi, tỷ lệ sản phẩm lỗi giảm xuống còn 1,5%.
-Các đường ống vận chuyển ở khu xử lý Fallen Grave đã được tối ưu hóa để đảm bảo chuyển giao tần số tái chế đến Energy Hub hiệu quả hơn.
+          <t>Sản lượng Echo ở Anima Cradle đã tăng gấp đôi, tỷ lệ sản phẩm lỗi giảm xuống còn 1,5%.
+Các đường ống vận chuyển ở khu xử lý Fallen Grave đã được tối ưu hóa để đảm bảo chuyển giao tần số tái chế đến Trung Tâm Năng Lượng hiệu quả hơn.
 Công tác kiểm tra định kỳ tại trung tâm điều khiển Lumen Tower đã hoàn tất, không phát hiện bất thường nào.</t>
         </is>
       </c>
@@ -19628,7 +19628,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Void Storm Zone I tại vùng biên giới giữa Etching Plains và Fangspire Chasm. Bên trong, mọi tàn tích đều bị bóp méo thành những tiếng vọng khúc xạ của Vật Chất Hư Không, rồi tái sinh vào thế giới này...</t>
+          <t>Khu Vực Bão Hư Không I tại vùng biên giới giữa Etching Plains và Fangspire Chasm. Bên trong, mọi tàn tích đều bị bóp méo thành những tiếng vọng khúc xạ của Vật Chất Hư Không, rồi tái sinh vào thế giới này...</t>
         </is>
       </c>
     </row>
@@ -19693,7 +19693,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Void Storm Zone II tại Exospine Barrows (Emberfall Barrows). Bên trong, mọi tàn tích đều bị bóp méo thành những tiếng vọng khúc xạ của Vật Chất Hư Không, rồi tái sinh vào thế giới này...</t>
+          <t>Khu Vực Bão Hư Không II tại Exospine Barrows (Emberfall Barrows). Bên trong, mọi tàn tích đều bị bóp méo thành những tiếng vọng khúc xạ của Vật Chất Hư Không, rồi tái sinh vào thế giới này...</t>
         </is>
       </c>
     </row>
@@ -19759,8 +19759,8 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Void Storm Zone III tại Sundermere. Bên trong, mọi tàn tích đều bị bóp méo thành những tiếng vọng khúc xạ của Vật Chất Hư Không, rồi tái sinh vào thế giới này...
-&lt;color=#c25757&gt;*Zone này có thử thách khó khăn. Khuyến nghị trang bị Antivoid Tactics: Antivoid Armor cho Expedition Motorbike trước khi tiến vào.&lt;/color&gt;</t>
+          <t>Khu Vực Bão Hư Không III tại Sundermere. Bên trong, mọi tàn tích đều bị bóp méo thành những tiếng vọng khúc xạ của Vật Chất Hư Không, rồi tái sinh vào thế giới này...
+&lt;color=#c25757&gt;*Khu vực này có thử thách khó khăn. Khuyến nghị trang bị Antivoid Tactics: Antivoid Armor cho Expedition Motorbike trước khi tiến vào.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -19825,7 +19825,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Void Storm Zone V tại vùng biên giới giữa Etching Plains và Startorch Academy. Bên trong, mọi tàn tích đều bị bóp méo thành những tiếng vọng khúc xạ của Vật Chất Hư Không, rồi tái sinh vào thế giới này...</t>
+          <t>Khu Vực Bão Hư Không V tại vùng biên giới giữa Etching Plains và Startorch Academy. Bên trong, mọi tàn tích đều bị bóp méo thành những tiếng vọng khúc xạ của Vật Chất Hư Không, rồi tái sinh vào thế giới này...</t>
         </is>
       </c>
     </row>
@@ -19891,8 +19891,8 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Void Storm Zone VI tại Stagnant Run. Bên trong, mọi tàn tích đều bị bóp méo thành những tiếng vọng khúc xạ của Vật Chất Hư Không, rồi tái sinh vào thế giới này...
-&lt;color=#c25757&gt;*Zone này ẩn chứa thử thách cực kỳ khó khăn. Khuyến nghị trang bị Antivoid Armor cho Xe Thám Hiểm trước khi tiến vào.&lt;/color&gt;</t>
+          <t>Khu Vực Bão Hư Không VI tại Stagnant Run. Bên trong, mọi tàn tích đều bị bóp méo thành những tiếng vọng khúc xạ của Vật Chất Hư Không, rồi tái sinh vào thế giới này...
+&lt;color=#c25757&gt;*Khu vực này ẩn chứa thử thách cực kỳ khó khăn. Khuyến nghị trang bị Antivoid Armor cho Xe Thám Hiểm trước khi tiến vào.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Void Storm Zone II tại vùng đất giữa Tidelost Forest và Wavecleave Cape. Bên trong, mọi tàn tích đều bị bóp méo thành những tiếng vọng khúc xạ của Vật Chất Hư Không, rồi tái sinh vào thế giới này...</t>
+          <t>Khu Vực Bão Hư Không II tại vùng đất giữa Tidelost Forest và Wavecleave Cape. Bên trong, mọi tàn tích đều bị bóp méo thành những tiếng vọng khúc xạ của Vật Chất Hư Không, rồi tái sinh vào thế giới này...</t>
         </is>
       </c>
     </row>
@@ -20022,7 +20022,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Void Storm Zone III tại vùng đất giữa Mount Gjallar và Ginnungamere Void Storm Monitoring Zone. Bên trong, mọi tàn tích đều bị bóp méo thành những tiếng vọng khúc xạ của Vật Chất Hư Không, rồi tái sinh vào thế giới này...</t>
+          <t>Khu Vực Bão Hư Không III tại vùng đất giữa Mount Gjallar và Ginnungamere Void Storm Monitoring Zone. Bên trong, mọi tàn tích đều bị bóp méo thành những tiếng vọng khúc xạ của Vật Chất Hư Không, rồi tái sinh vào thế giới này...</t>
         </is>
       </c>
     </row>
@@ -20088,8 +20088,8 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Void Storm Zone IV tại Frostlands Transit Port. Bên trong, mọi tàn tích đều bị bóp méo thành những tiếng vọng khúc xạ của Vật Chất Hư Không, rồi tái sinh vào thế giới này...
-&lt;color=#c25757&gt;*Zone này có thử thách khó khăn. Khuyến nghị trang bị Antivoid Tactics: Antivoid Armor cho Expedition Motorbike trước khi tiến vào.&lt;/color&gt;</t>
+          <t>Khu Vực Bão Hư Không IV tại Frostlands Transit Port. Bên trong, mọi tàn tích đều bị bóp méo thành những tiếng vọng khúc xạ của Vật Chất Hư Không, rồi tái sinh vào thế giới này...
+&lt;color=#c25757&gt;*Khu vực này có thử thách khó khăn. Khuyến nghị trang bị Antivoid Tactics: Antivoid Armor cho Expedition Motorbike trước khi tiến vào.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -20155,8 +20155,8 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Void Storm Zone V tại vùng biên giới giữa Upphaf Forest Ruins và Provenance Enclave. Bên trong, mọi tàn tích đều bị bóp méo thành những tiếng vọng khúc xạ của Vật Chất Hư Không, rồi tái sinh vào thế giới này...
-&lt;color=#c25757&gt;*Zone này có thử thách khó khăn. Khuyến nghị trang bị Antivoid Tactics: Antivoid Armor cho Expedition Motorbike trước khi tiến vào.&lt;/color&gt;</t>
+          <t>Khu Vực Bão Hư Không V tại vùng biên giới giữa Upphaf Forest Ruins và Provenance Enclave. Bên trong, mọi tàn tích đều bị bóp méo thành những tiếng vọng khúc xạ của Vật Chất Hư Không, rồi tái sinh vào thế giới này...
+&lt;color=#c25757&gt;*Khu vực này có thử thách khó khăn. Khuyến nghị trang bị Antivoid Tactics: Antivoid Armor cho Expedition Motorbike trước khi tiến vào.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -20222,8 +20222,8 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Một số Soliskin đã mất đi sự dẫn dắt của Shepherd và giờ đây lang thang ở Lahai-Roi.
-Hãy tìm kiếm những Soliskin lạc lối này và mang những hạt Soliseed thu thập được đến Soliseed Plains. Tại đó, Giant Soliskin sẽ chuyển hóa năng lượng từ Soliseed trở lại Mái Solvein Canopy, giúp những Soliskin mới được sinh ra.</t>
+          <t>Một số Soliskin đã mất đi sự dẫn dắt của Người Chăn Cừu và giờ đây lang thang ở Lahai-Roi.
+Hãy tìm kiếm những Soliskin lạc lối này và mang những hạt Soliseed thu thập được đến Đồng Bằng Soliseed. Tại đó, Soliskin Khổng Lồ sẽ chuyển hóa năng lượng từ Soliseed trở lại Mái Vòm Solvein, giúp những Soliskin mới được sinh ra.</t>
         </is>
       </c>
     </row>
@@ -20631,7 +20631,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>"...Do sự gia tăng gần đây của các hiện tượng thời tiết nguy hiểm tại Etching Plains, việc vận hành thủ công truyền thống để sửa chữa cơ sở hạ tầng tiềm ẩn nguy cơ an toàn nghiêm trọng. Vì vậy, giao thức vận hành thông minh hoàn toàn tự động đang được kích hoạt..."</t>
+          <t>"...Do sự gia tăng gần đây của các hiện tượng thời tiết nguy hiểm tại Đồng Bằng Khắc Tạc, việc vận hành thủ công truyền thống để sửa chữa cơ sở hạ tầng tiềm ẩn nguy cơ an toàn nghiêm trọng. Vì vậy, giao thức vận hành thông minh hoàn toàn tự động đang được kích hoạt..."</t>
         </is>
       </c>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Minna vừa mua chiếc Terminal đầu tiên trong đời, nhưng cô bé dường như chẳng biết dùng nó như thế nào...
+          <t>Minna vừa mua chiếc Thiết bị đầu cuối đầu tiên trong đời, nhưng cô bé dường như chẳng biết dùng nó như thế nào...
 Hãy tìm gặp cô ở Bjartr Woods và giúp đỡ trước khi cô vô tình làm hỏng nó.</t>
         </is>
       </c>
@@ -20828,7 +20828,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Cậu đã thu hút sự chú ý của một trợ lý Terminal cực kỳ tinh ý. Hắn ta khẳng định có một đường đua mà chưa ai từng cán đích...</t>
+          <t>Cậu đã thu hút sự chú ý của một trợ lý Thiết bị đầu cuối cực kỳ tinh ý. Hắn ta khẳng định có một đường đua mà chưa ai từng cán đích...</t>
         </is>
       </c>
     </row>
@@ -20959,8 +20959,8 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Một số Soliskin đã mất đi sự dẫn dắt của Shepherd và giờ đây lang thang ở Lahai-Roi.
-Hãy tìm kiếm những Soliskin lạc lối này và mang những hạt Soliseed thu thập được đến Soliseed Plains. Tại đó, Giant Soliskin sẽ chuyển hóa năng lượng từ Soliseed trở lại Mái Solvein Canopy, giúp những Soliskin mới được sinh ra.</t>
+          <t>Một số Soliskin đã mất đi sự dẫn dắt của Người Chăn Cừu và giờ đây lang thang ở Lahai-Roi.
+Hãy tìm kiếm những Soliskin lạc lối này và mang những hạt Soliseed thu thập được đến Đồng Bằng Soliseed. Tại đó, Soliskin Khổng Lồ sẽ chuyển hóa năng lượng từ Soliseed trở lại Mái Vòm Solvein, giúp những Soliskin mới được sinh ra.</t>
         </is>
       </c>
     </row>
@@ -21091,8 +21091,8 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Một số Soliskin đã mất đi sự dẫn dắt của Shepherd và giờ đây lang thang trên Bề Mặt Vùng Đất Băng Giá.
-Hãy tìm kiếm những Soliskin lạc lối này và mang những hạt Soliseed thu thập được đến Giant Soliskin trong Phòng Sinh Mệnh Upphaf.</t>
+          <t>Một số Soliskin đã mất đi sự dẫn dắt của Người Chăn Cừu và giờ đây lang thang trên Bề Mặt Vùng Đất Băng Giá.
+Hãy tìm kiếm những Soliskin lạc lối này và mang những hạt Soliseed thu thập được đến Soliskin Khổng Lồ trong Phòng Sinh Mệnh Upphaf.</t>
         </is>
       </c>
     </row>
@@ -21222,7 +21222,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Sau khi nghe tin "Quý Cô Miko" có thể có liên hệ với Special Response Force, cô ấy bảo cậu nên tham khảo I.R.I.S. trong khi cô tiếp tục thu thập thông tin quanh trường.</t>
+          <t>Sau khi nghe tin "Quý Cô Miko" có thể có liên hệ với Lực Lượng Đặc Nhiệm, cô ấy bảo cậu nên tham khảo I.R.I.S. trong khi cô tiếp tục thu thập thông tin quanh trường.</t>
         </is>
       </c>
     </row>
@@ -21677,7 +21677,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Void Storm Zone III tại Sealed Fissure. Bên trong, mọi tàn tích đều bị bóp méo thành những tiếng vọng khúc xạ của Vật Chất Hư Không, rồi tái sinh vào thế giới này...</t>
+          <t>Khu Vực Bão Hư Không III tại Sealed Fissure. Bên trong, mọi tàn tích đều bị bóp méo thành những tiếng vọng khúc xạ của Vật Chất Hư Không, rồi tái sinh vào thế giới này...</t>
         </is>
       </c>
     </row>
@@ -21742,7 +21742,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Trạm nghiên cứu khoa học do Startorch Academy và Bộ tộc Roya hợp tác xây dựng. Trại căn cứ này cung cấp đầy đủ hỗ trợ hậu cần và hoạt động cho các cuộc thám hiểm thực địa. Với các thiết bị quan sát, lấy mẫu, thí nghiệm, liên lạc, lưu trữ năng lượng và hỗ trợ sự sống, nó là nơi trú ẩn giúp các nhà nghiên cứu làm việc an toàn và ổn định trong những chiến dịch dài hạn tại Dimmr Plains.</t>
+          <t>Trạm nghiên cứu khoa học do Học viện Startorch và Bộ tộc Roya hợp tác xây dựng. Trại căn cứ này cung cấp đầy đủ hỗ trợ hậu cần và hoạt động cho các cuộc thám hiểm thực địa. Với các thiết bị quan sát, lấy mẫu, thí nghiệm, liên lạc, lưu trữ năng lượng và hỗ trợ sự sống, nó là nơi trú ẩn giúp các nhà nghiên cứu làm việc an toàn và ổn định trong những chiến dịch dài hạn tại Đồng bằng Dimmr.</t>
         </is>
       </c>
     </row>
@@ -21872,7 +21872,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Dù Threnodian đã biến mất, bóng tối của nó vẫn còn vương vấn. Hãy giúp Spacetrek Collective tiêu diệt những mối đe dọa không ngừng trên Dimmr Plains. Có vẻ như những lưỡi kiếm băng tìm thấy trên đồng bằng có thể được sử dụng như công cụ mạnh mẽ...</t>
+          <t>Dù Threnodian đã biến mất, bóng tối của nó vẫn còn vương vấn. Hãy giúp Tập Đoàn Spacetrek tiêu diệt những mối đe dọa không ngừng trên Đồng Bằng Dimmr. Có vẻ như những lưỡi kiếm băng tìm thấy trên đồng bằng có thể được sử dụng như công cụ mạnh mẽ...</t>
         </is>
       </c>
     </row>
@@ -21937,7 +21937,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Bộ Lưu Trữ Light là thành phần lưu trữ dữ liệu nhạy sáng của Exostrider, có thể được cung cấp năng lượng bởi Soliskin. Điều chỉnh hình chiếu của nó về dạng chính xác để kích hoạt thiết bị.</t>
+          <t>Bộ Lưu Trữ Ánh Sáng là thành phần lưu trữ dữ liệu nhạy sáng của Exostrider, có thể được cung cấp năng lượng bởi Soliskin. Điều chỉnh hình chiếu của nó về dạng chính xác để kích hoạt thiết bị.</t>
         </is>
       </c>
     </row>
@@ -22002,7 +22002,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Thử thách Dodge các khối rơi. Lấy cảm hứng từ một trò chơi kinh điển, cậu cần lấp đầy một hàng để xóa nó. Giữ vững vị trí đủ lâu, chiến thắng sẽ thuộc về cậu.</t>
+          <t>Thử thách né các khối rơi. Lấy cảm hứng từ một trò chơi kinh điển, cậu cần lấp đầy một hàng để xóa nó. Giữ vững vị trí đủ lâu, chiến thắng sẽ thuộc về cậu.</t>
         </is>
       </c>
     </row>
@@ -22069,7 +22069,7 @@
       <c r="M322" t="inlineStr">
         <is>
           <t>Tiến lên trên đường đua đã chọn, vượt qua mọi chướng ngại vật và kiếm đủ điểm để hoàn thành thử thách.
-Sử dụng Drift để trượt dưới rào chắn hoặc Bounce Nhảy để nhảy qua chướng ngại. Cậu cũng có thể dùng Drift để điều khiển xe máy lượn qua một số vị trí nhằm kiếm thêm điểm.</t>
+Sử dụng Drift để trượt dưới rào chắn hoặc Bounce Jump để nhảy qua chướng ngại. Cậu cũng có thể dùng Drift để điều khiển xe máy lượn qua một số vị trí nhằm kiếm thêm điểm.</t>
         </is>
       </c>
     </row>
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Tại Khu Rừng Hoàng Hôn trên Dimmr Plains, nguyên mẫu Helios—từng bị mất tích trong một cơn Void Storm—nay nằm đây trong giấc ngủ im lặng. Nó đã đồng hành cùng bao thế hệ Soliskin trong những cuộc hành trình và chứng kiến tấm lòng trong sáng của những nhà nghiên cứu đầu tiên.</t>
+          <t>Tại Khu Rừng Hoàng Hôn trên Đồng Bằng Dimmr, nguyên mẫu Helios—từng bị mất tích trong một cơn Bão Hư Không—nay nằm đây trong giấc ngủ im lặng. Nó đã đồng hành cùng bao thế hệ Soliskin trong những cuộc hành trình và chứng kiến tấm lòng trong sáng của những nhà nghiên cứu đầu tiên.</t>
         </is>
       </c>
     </row>
@@ -22199,7 +22199,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Một số Soliskin đã mất đi sự dẫn dắt của Shepherd và giờ đây lang thang trên Dimmr Plains. Hãy tìm kiếm những Soliskin lạc lối này và mang những hạt Soliseed thu thập được đến Giant Soliskin tại Bến Đáp Solisia.</t>
+          <t>Một số Soliskin đã mất đi sự dẫn dắt của Người Chăn Cừu và giờ đây lang thang trên Đồng Bằng Dimmr. Hãy tìm kiếm những Soliskin lạc lối này và mang những hạt Soliseed thu thập được đến Soliskin Khổng Lồ tại Bến Đáp Solisia.</t>
         </is>
       </c>
     </row>
@@ -22399,7 +22399,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Uncle Fu bảo chú có một món đồ thần kỳ.
+          <t>Chú Phú bảo chú có một món đồ thần kỳ.
 Nghe nói món đồ này có hình dáng như một chiếc vảy và mang sức mạnh ma thuật tên là Chrono Trace, có thể giúp người ta sống lại những khoảnh khắc trong quá khứ...</t>
         </is>
       </c>
@@ -22466,8 +22466,8 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>"Cậu đã nghe chưa? Dưới gốc Cây Wish có một nơi mà những giấc mơ được chắp cánh bay xa. Người ta gọi đó là Lữ Quán Trăng Rằm."
-Khi trăng tròn dần, Jinzhou rộn ràng trong không khí chuẩn bị cho Moon-Chasing Festival. Đây là truyền thống yêu dấu, nơi bạn bè và gia đình quây quần cùng gửi gắm ước nguyện lên bầu trời đêm. Trước khi lễ hội bắt đầu, những lời thì thầm về Lữ Quán Trăng Rằm – nơi ước nguyện thành hiện thực – đã lọt vào tai cậu. Tò mò, cậu quyết định...</t>
+          <t>"Cậu đã nghe chưa? Dưới gốc Cây Ước Nguyện có một nơi mà những giấc mơ được chắp cánh bay xa. Người ta gọi đó là Lữ Quán Trăng Rằm."
+Khi trăng tròn dần, Jinzhou rộn ràng trong không khí chuẩn bị cho Lễ Hội Đuổi Trăng. Đây là truyền thống yêu dấu, nơi bạn bè và gia đình quây quần cùng gửi gắm ước nguyện lên bầu trời đêm. Trước khi lễ hội bắt đầu, những lời thì thầm về Lữ Quán Trăng Rằm – nơi ước nguyện thành hiện thực – đã lọt vào tai cậu. Tò mò, cậu quyết định...</t>
         </is>
       </c>
     </row>
@@ -22533,8 +22533,8 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>"Cậu đã nghe chưa? Dưới gốc Cây Wish có một nơi mà những giấc mơ được chắp cánh bay xa. Người ta gọi đó là Lữ Quán Trăng Rằm."
-Khi trăng tròn dần, Jinzhou rộn ràng trong không khí chuẩn bị cho Moon-Chasing Festival. Đây là truyền thống yêu dấu, nơi bạn bè và gia đình quây quần cùng gửi gắm ước nguyện lên bầu trời đêm. Trước khi lễ hội bắt đầu, những lời thì thầm về Lữ Quán Trăng Rằm – nơi ước nguyện thành hiện thực – đã lọt vào tai cậu. Tò mò, cậu quyết định...</t>
+          <t>"Cậu đã nghe chưa? Dưới gốc Cây Ước Nguyện có một nơi mà những giấc mơ được chắp cánh bay xa. Người ta gọi đó là Lữ Quán Trăng Rằm."
+Khi trăng tròn dần, Jinzhou rộn ràng trong không khí chuẩn bị cho Lễ Hội Đuổi Trăng. Đây là truyền thống yêu dấu, nơi bạn bè và gia đình quây quần cùng gửi gắm ước nguyện lên bầu trời đêm. Trước khi lễ hội bắt đầu, những lời thì thầm về Lữ Quán Trăng Rằm – nơi ước nguyện thành hiện thực – đã lọt vào tai cậu. Tò mò, cậu quyết định...</t>
         </is>
       </c>
     </row>
@@ -22601,8 +22601,8 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Bạn tìm thấy Cosmos, người bạn lông lá của Encore, bên cạnh một cánh cổng bí ẩn. Có vẻ như một loại thử nghiệm đang diễn ra phía sau cánh cổng và cần sự trợ giúp của bạn.
-Trong thử nghiệm, Cosmos sẽ cung cấp Echoid để tăng cường đáng kể sức mạnh chiến đấu của Resonators.
+          <t>Bạn tìm thấy Cosmos, người bạn lông lá của Encore, bên cạnh một cánh cổng bí ẩn. Có vẻ như một bài kiểm tra nào đó đang diễn ra phía sau cánh cổng và cần sự trợ giúp của bạn.
+Trong quá trình kiểm tra, Cosmos sẽ cung cấp Echoid để tăng cường đáng kể sức chiến đấu của Resonator.
 Bạn có thể hoàn thành nhiệm vụ cùng bạn bè.</t>
         </is>
       </c>
@@ -22941,7 +22941,7 @@
         <is>
           <t>Rover thân mến,
 Phần mới nhất của Depths of Illusive Realm đã có mặt.
-Hoàn thành các thử thách mới để mở khóa vật phẩm mới trong Illusive Cửa hàng.
+Hoàn thành các thử thách mới để mở khóa vật phẩm mới trong Illusive Store.
 Khi bạn đã sẵn sàng, hãy đến Depths of Illusive Realm để đối mặt với hỗn loạn một lần nữa.</t>
         </is>
       </c>
@@ -23012,7 +23012,7 @@
         <is>
           <t>Rover thân mến,
 Phần mới nhất của Depths of Illusive Realm đã có mặt.
-Hoàn thành các thử thách mới để mở khóa vật phẩm mới trong Illusive Cửa hàng.
+Hoàn thành các thử thách mới để mở khóa vật phẩm mới trong Illusive Store.
 Khi bạn đã sẵn sàng, hãy đến Depths of Illusive Realm để đối mặt với hỗn loạn một lần nữa.</t>
         </is>
       </c>
@@ -23218,7 +23218,7 @@
       <c r="M339" t="inlineStr">
         <is>
           <t>Trong lúc ở Jinzhou, cậu tình cờ gặp Encore đang đi nghỉ mát. Cô ấy gửi lời mời đặc biệt đến cậu—
-Cuộc phiêu lưu sắp bắt đầu! Là người bạn thân thiết nhất của cô ấy, cậu có muốn cùng Wooly Warrior bước vào chuyến hành trình thú vị này không?</t>
+Cuộc phiêu lưu sắp bắt đầu! Là người bạn thân thiết nhất của cô ấy, cậu có muốn cùng Chiến Binh Lông Xù bước vào chuyến hành trình thú vị này không?</t>
         </is>
       </c>
     </row>
@@ -23284,7 +23284,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Arno, đặc vụ của Black Shores, hiện đang tìm kiếm sự hỗ trợ để thu thập Surveillance Dataset tại Lament với phần thưởng hậu hĩnh.
+          <t>Arno, đặc vụ của Black Shores, hiện đang tìm kiếm sự hỗ trợ để thu thập Bộ Dữ Liệu Giám Sát tại Lament với phần thưởng hậu hĩnh.
 Địa hình hiểm trở đòi hỏi phản xạ nhạy bén và kỹ năng móc nối điêu luyện. Nếu đây là nhiệm vụ hợp gu cậu, hãy tìm gặp hắn để biết thêm chi tiết.</t>
         </is>
       </c>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Sau Trận chiến Norfall Barrens, Black Shores và Huaxu Academy đã hợp tác phát triển Infinite Battle Simulation, một hệ thống huấn luyện mô phỏng nhằm đối phó với những mối đe dọa tiềm tàng từ tần số còn sót lại của Threnody.</t>
+          <t>Sau Trận chiến tại Norfall Barrens, Bờ Biển Đen và Học viện Huaxu đã hợp tác phát triển Hệ thống Mô phỏng Chiến đấu Vô hạn, một hệ thống huấn luyện mô phỏng nhằm đối phó với những mối đe dọa tiềm tàng từ tần số còn sót lại của Threnodian.</t>
         </is>
       </c>
     </row>
@@ -23482,9 +23482,9 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Bên cạnh một cánh cổng bí ẩn là cô gái Dorothy, vô tình lạc qua đó. Cô ấy cần sự giúp đỡ của bạn để đánh bại những con quái vật ẩn nấp sau cánh cổng.
-Trong thử thách này, bạn có thể chọn "Dorothy's Companions" làm Echoes hỗ trợ trong trận chiến, giúp tăng cường đáng kể sức mạnh chiến đấu của Resonators.
-Bạn có thể hoàn thành nhiệm vụ cùng Bạn bè.</t>
+          <t>Bên cạnh cánh cổng huyền bí là một cô bé vô tình lạc qua đó—Dorothy. Cô bé cầu cứu cậu giúp đánh bại lũ quái vật đang ẩn nấp phía sau.
+Trong thử thách này, cậu có thể chọn "Bạn Đồng Hành của Dorothy" làm Echo hỗ trợ chiến đấu, giúp tăng cường đáng kể khả năng chiến đấu của Resonator.
+Cậu có thể hoàn thành nhiệm vụ cùng bạn bè của mình.</t>
         </is>
       </c>
     </row>
@@ -23621,8 +23621,8 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Hoàn thành Pioneer Project để nhận những phần thưởng tuyệt vời.
-Sau khi bản cập nhật chính thức ra mắt, phần thưởng nhận được từ Pioneer Project sẽ được gửi đến tài khoản của bạn trên máy chủ chính thức trong vòng 14 ngày làm việc.</t>
+          <t>Hoàn thành Dự Án Tiên Phong để nhận những phần thưởng tuyệt vời.
+Sau khi bản cập nhật chính thức ra mắt, phần thưởng nhận được từ Dự Án Tiên Phong sẽ được gửi đến tài khoản của bạn trên máy chủ chính thức trong vòng 14 ngày làm việc.</t>
         </is>
       </c>
     </row>
@@ -23687,7 +23687,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Để khuyến khích các Pioneer chia sẻ thêm về những chuyến thám hiểm Jinzhou, Lollo Logistics đã hợp tác với Pioneer Association hân hạnh giới thiệu chiến dịch: Beyond the Waves! Tham gia và tải Adventure Logs của bạn lên xe tải chuyển phát Lollo để nhận nhiều Adventure Packages đa dạng!</t>
+          <t>Để khuyến khích các Pioneer chia sẻ thêm về những chuyến thám hiểm Jinzhou, Lollo Logistics đã hợp tác với Hiệp hội Pioneer hân hạnh giới thiệu chiến dịch: Beyond the Waves! Tham gia và tải Adventure Logs của bạn lên xe tải chuyển phát Lollo để nhận nhiều Adventure Packages đa dạng!</t>
         </is>
       </c>
     </row>
@@ -23886,9 +23886,9 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Bên cạnh một bức tranh morph bí ẩn, bạn gặp một họa sĩ tên Claudia, bị mắc kẹt trong những cơn ác mộng của cô.
-Claudia nhờ bạn điều tra thế giới bên trong bức tranh và đưa cho bạn một lá bùa hộ mệnh. Trong thế giới tranh vẽ, lá bùa biến thành nhiều Echoes khác nhau để hỗ trợ bạn.
-Bạn có thể hoàn thành nhiệm vụ cùng bạn bè.</t>
+          <t>Bên cạnh bức tranh biến ảo kỳ bí, bạn tìm thấy một họa sĩ tên Claudia, bị mắc kẹt trong những cơn ác mộng của chính mình. 
+Claudia nhờ bạn điều tra thế giới bên trong bức tranh và trao cho bạn một lá bùa hộ mệnh. Trong thế giới hội họa, lá bùa biến thành những Echo khác nhau để hỗ trợ bạn.
+Bạn có thể hoàn thành nhiệm vụ này cùng bạn bè.</t>
         </is>
       </c>
     </row>
@@ -24021,8 +24021,8 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;(Chương II Nhiệm vụ Main hiện đã mở khóa, người chơi đủ điều kiện có thể trải nghiệm chương này sớm.)&lt;/color&gt;
-Hỡi Rover được dòng chảy dẫn lối, ngươi đã xua tan bóng tối chiến tranh ở Jinzhou và vượt qua ranh giới thời gian trên đỉnh Núi Firmament. Khi đứng trên bờ biển cô tịch, ngươi có nghe thấy lời phúc âm vang trên cơn gió bão, vọng khắp biển động không? Ngươi có thoáng thấy vẻ huy hoàng vô song ẩn giấu trong vùng đất huyền thoại của những Echo? Giờ đây, hãy tôi rèn lòng dũng cảm, dấn thân vào miền đất vô định, đương đầu với bão tố và mở đường đến Rinascita.</t>
+          <t>&lt;color=Highlight&gt;(Chương II Nhiệm vụ Chính hiện đã mở khóa, người chơi đủ điều kiện có thể trải nghiệm chương này sớm.)&lt;/color&gt;
+Hỡi Vận Mệnh Giả được dòng chảy dẫn lối, ngươi đã xua tan bóng tối chiến tranh ở Jinzhou và vượt qua ranh giới thời gian trên đỉnh Núi Firmament. Khi đứng trên bờ biển cô tịch, ngươi có nghe thấy lời phúc âm vang trên cơn gió bão, vọng khắp biển động không? Ngươi có thoáng thấy vẻ huy hoàng vô song ẩn giấu trong vùng đất huyền thoại của những Tiếng Vọng? Giờ đây, hãy tôi rèn lòng dũng cảm, dấn thân vào miền đất vô định, đương đầu với bão tố và mở đường đến Rinascita.</t>
         </is>
       </c>
     </row>
@@ -24156,7 +24156,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Sau khi vượt qua màn sương biển nguy hiểm và những con sóng dữ dội, cuối cùng ngươi đã đặt chân đến Rinascita, Land of Echoes.
+          <t>Sau khi vượt qua màn sương biển nguy hiểm và những con sóng dữ dội, cuối cùng ngươi đã đặt chân đến Rinascita, Vùng Đất Tiếng Vọng.
 Những ánh sáng rực rỡ trải dài khắp chân trời, trong khi những giai điệu vui tươi vang vọng khắp vịnh và những cánh đồng hoa.
 Lễ hội Carnevale sắp đến gần. Mong rằng hành trình của ngươi sẽ là một chuyến phiêu lưu đáng nhớ.</t>
         </is>
@@ -24223,7 +24223,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>"Vị khách quý từ phương xa, xin thứ lỗi cho sự đường đột của ta, nhưng chúng tôi đang rất cần sự giúp đỡ của ngài. Ngài là người duy nhất có thể khuất phục được Terminal bị nhiễm tà ác đó..." Nơi xa xôi ngoài thành Ragunna, một bóng tối lay động, thì thầm nguy hiểm. Lời cầu cứu của người vô tội đè nặng trong lòng, và ngươi không thể đứng yên...</t>
+          <t>"Vị khách quý từ phương xa, xin thứ lỗi cho sự đường đột của ta, nhưng chúng tôi đang rất cần sự giúp đỡ của ngài. Ngài là người duy nhất có thể khuất phục được Thiết bị đầu cuối bị nhiễm tà ác đó..." Nơi xa xôi ngoài thành Ragunna, một bóng tối lay động, thì thầm nguy hiểm. Lời cầu cứu của người vô tội đè nặng trong lòng, và ngươi không thể đứng yên...</t>
         </is>
       </c>
     </row>
@@ -24353,7 +24353,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Những "người hành hương" lưu đày thực sự cần gì? Food? Nơi trú ẩn? Hay có lẽ, một tia sáng sao giữa bầu trời đêm, một biểu tượng của hy vọng? Giờ đây, khi có Roccia bên cạnh, đã đến lúc đi tìm thứ ánh sáng đó...</t>
+          <t>Những "người hành hương" lưu đày thực sự cần gì? Thức ăn? Nơi trú ẩn? Hay có lẽ, một tia sáng sao giữa bầu trời đêm, một biểu tượng của hy vọng? Giờ đây, khi có Roccia bên cạnh, đã đến lúc đi tìm thứ ánh sáng đó...</t>
         </is>
       </c>
     </row>
@@ -24552,7 +24552,7 @@
         <is>
           <t>Rover thân mến,
 Lễ hội Dances For Spring's Return sắp kết thúc. Đừng ngần ngại tham gia và nhận phần thưởng sự kiện của bạn nhé. Cảm ơn vì đã ủng hộ!
-Lưu ý rằng Trang phục "Exorcistic Adjuration" của Sanhua, hiện có thể nhận trong phần thưởng sự kiện, sẽ được bán với giá gốc tại Trang phục Cửa hàng sau bản cập nhật tiếp theo.</t>
+Lưu ý rằng Trang phục "Exorcistic Adjuration" của Sanhua, hiện có thể nhận trong phần thưởng sự kiện, sẽ được bán với giá gốc tại Cửa hàng Trang phục sau bản cập nhật tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -24682,7 +24682,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Lollo Logistics một lần nữa hợp tác với Pioneer Association mang đến chiến dịch thú vị: Beyond the Waves! Chỉ cần tải Nhật Ký Phiêu Lưu của cậu lên xe chuyển phát, và cậu sẽ nhận được "Gói Phiêu Lưu" đầy bất ngờ tại mỗi địa điểm!</t>
+          <t>Lollo Logistics một lần nữa hợp tác với Hiệp Hội Tiên Phong mang đến chiến dịch thú vị: Beyond the Waves! Chỉ cần tải Nhật Ký Phiêu Lưu của cậu lên xe chuyển phát, và cậu sẽ nhận được "Gói Phiêu Lưu" đầy bất ngờ tại mỗi địa điểm!</t>
         </is>
       </c>
     </row>
@@ -24747,7 +24747,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Lollo Logistics một lần nữa hợp tác với Pioneer Association hân hạnh giới thiệu chiến dịch phong phú: Beyond the Waves! Chỉ cần tải Nhật Ký Phiêu Lưu của cậu lên chiếc xe chuyển phát này, và cậu sẽ nhận được "Gói Phiêu Lưu" tương ứng với địa điểm đó, chứa đầy bất ngờ!</t>
+          <t>Lollo Logistics một lần nữa hợp tác với Hiệp Hội Tiên Phong hân hạnh giới thiệu chiến dịch phong phú: Beyond the Waves! Chỉ cần tải Nhật Ký Phiêu Lưu của cậu lên chiếc xe chuyển phát này, và cậu sẽ nhận được "Gói Phiêu Lưu" tương ứng với địa điểm đó, chứa đầy bất ngờ!</t>
         </is>
       </c>
     </row>
@@ -24948,7 +24948,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>The Black Shores đã phát triển một chương trình huấn luyện đặc biệt, có thể mô phỏng những thử thách nguy hiểm trên Solaris bằng cách sử dụng dữ liệu hệ thống Tethys. Chương trình này là thước đo tốt cho khả năng chiến đấu của người thử thách trong điều kiện bất lợi.</t>
+          <t>Bờ Biển Đen đã phát triển một chương trình huấn luyện đặc biệt, có thể mô phỏng những thử thách nguy hiểm trên Solaris bằng cách sử dụng dữ liệu hệ thống Tethys. Chương trình này là thước đo tốt cho khả năng chiến đấu của người thử thách trong điều kiện bất lợi.</t>
         </is>
       </c>
     </row>
@@ -25015,7 +25015,7 @@
       <c r="M366" t="inlineStr">
         <is>
           <t>Một cánh cổng quen thuộc dẫn vào Somnoire đã xuất hiện tại Rinascita. Những ký ức xa xưa chôn sâu trong giấc mơ, và chìa khóa khám phá giờ nằm trong tay ngươi. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
-&lt;color=yellow&gt;(Challenge Combat Hàng Tuần New Đã Xuất Hiện. Hãy Thử Ngay!)&lt;/color&gt;</t>
+&lt;color=yellow&gt;(Thử Thách Chiến Đấu Hàng Tuần Mới Đã Xuất Hiện. Hãy Thử Ngay!)&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -25283,9 +25283,9 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Từ những người tạo ra *Second Coming of Solaris*, một kiệt tác được tái hiện!
+          <t>Từ những người tạo ra *Sự Trở Lại Của Solaris*, một kiệt tác được tái hiện!
 Bước vào thế giới kỳ diệu chưa từng thấy!
-Hãy đắm chìm trong *Second Coming of Solaris* và chứng kiến... chứ-chứng kiến... ssssssss...
+Hãy đắm chìm trong *Sự Trở Lại Của Solaris* và chứng kiến... chứ-chứng kiến... ssssssss...
 &lt;color=#ffd12f&gt;Để đảm bảo trải nghiệm trò chơi tốt nhất, một số câu chuyện trong sự kiện này không thể bỏ qua.&lt;/color&gt;</t>
         </is>
       </c>
@@ -25354,7 +25354,7 @@
       <c r="M371" t="inlineStr">
         <is>
           <t>Một cô gái tên Dorothy xuất hiện bên cạnh cánh cổng bí ẩn. Cô cho biết một cuộc khủng hoảng bất ngờ đang diễn ra bên trong.
-Trong thử thách này, bạn có thể chọn "Companions của Dorothy" làm Echoes để hỗ trợ trong trận chiến, giúp tăng cường đáng kể sức mạnh chiến đấu của Resonators.
+Trong thử thách này, bạn có thể chọn "Đồng Hành của Dorothy" làm Echo để hỗ trợ trong trận chiến, giúp tăng cường đáng kể sức mạnh chiến đấu của các Resonator.
 Bạn có thể hoàn thành nhiệm vụ cùng bạn bè.</t>
         </is>
       </c>
@@ -25421,7 +25421,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Rover thân mến,
+          <t>Vận Mệnh Giả thân mến,
 Sự kiện Dances For Spring's Return đã kết thúc. Phần thưởng sự kiện chưa nhận của bạn—Trang phục Sanhua "Exorcistic Adjuration"—đã được tự động thêm vào tài khoản. Bạn có thể xem nó trên trang Resonator.</t>
         </is>
       </c>
@@ -25557,7 +25557,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>KU-Ryan, một robot của Black Shores, hiện đang cần hỗ trợ thu thập Surveillance Dataset về Hiện Tượng Bị Sóng Xói Mòn tại Ragunna.
+          <t>KU-Ryan, một robot của Black Shores, hiện đang cần hỗ trợ thu thập Bộ Dữ Liệu Giám Sát về Hiện Tượng Bị Sóng Xói Mòn tại Ragunna.
 Địa hình hiểm trở đòi hỏi phản xạ nhạy bén và kỹ năng móc treo điêu luyện. Nếu đây là nhiệm vụ hợp gu cậu, hãy tìm gặp hắn để biết thêm chi tiết.</t>
         </is>
       </c>
@@ -25698,7 +25698,7 @@
         <is>
           <t>[Giai đoạn Ủng hộ]
 08:00 04/05/2025 đến 19:00 23/05/2025 (giờ máy chủ)
-[Giai đoạn Tính điểm Ranking]
+[Giai đoạn Tính điểm Xếp hạng]
 19:30 23/05/2025 đến 03:59 26/05/2025 (giờ máy chủ)
 Giải đấu Cube đầu tiên do Hiệp hội Tiên phong tổ chức đã chính thức khởi tranh! Mười hai ngôi sao Cube sẽ trổ tài trên đường đua, gác lại địa vị và thân phận, dốc sức tranh ngôi vị Cube nhanh nhất!
 Với những ai không thể tham gia trực tiếp, đừng lo! Chúng tôi đã chuẩn bị sẵn sàng! Bạn có thể ủng hộ những ứng cử viên tiềm năng qua các kênh chính thức! Ngoài ra, Hiệp hội Tiên phong sẽ phát sóng trực tiếp toàn bộ sự kiện, mời tất cả mọi người cùng theo dõi và cổ vũ cho thí sinh mình yêu thích!
@@ -25835,7 +25835,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Lễ hội sắp bắt đầu. Invite bạn bè của bạn trở lại để cùng tham gia vui chơi tại Rinascita. Hoàn thành nhiệm vụ cùng nhau để nhận Astrites và các phần thưởng khác!
+          <t>Lễ hội sắp bắt đầu. Mời bạn bè của bạn trở lại để cùng tham gia vui chơi tại Rinascita. Hoàn thành nhiệm vụ cùng nhau để nhận Astrites và các phần thưởng khác!
 &lt;color=yellow&gt;(Truy cập trang sự kiện để xem mã mời)&lt;/color&gt;</t>
         </is>
       </c>
@@ -25902,8 +25902,8 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>KU-Lolo vừa nảy ra ý tưởng mới để biến những kỷ niệm yêu thích của cậu thành những Cube lưu niệm độc đáo trong Second Coming of Solaris!
-&lt;color=#ffd12f&gt;Hoàn thành Nhiệm Vụ Sự Kiện "Cube, Vuông Vắn Và Dễ Thương" để có trải nghiệm tuyệt vời nhất.&lt;/color&gt;</t>
+          <t>KU-Lolo vừa nảy ra ý tưởng mới để biến những kỷ niệm yêu thích của cậu thành những Khối Lập Phương lưu niệm độc đáo trong Sự Trở Lại Của Solaris!
+&lt;color=#ffd12f&gt;Hoàn thành Nhiệm Vụ Sự Kiện "Khối Lập Phương, Vuông Vắn Và Dễ Thương" để có trải nghiệm tuyệt vời nhất.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -26034,8 +26034,8 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Chào mừng! Chương trình đặc biệt của Wutherium Film Studio: "Resonators Trong Trận Chiến" đã chính thức ra mắt!
-Ghi lại những khoảnh khắc hào hùng của Resonators trong trận chiến, rồi gửi ảnh cho Fulmine và C-MOSS để nhận về vô vàn phần thưởng!</t>
+          <t>Chào mừng! Chương trình đặc biệt của Wutherium Film Studio: "Resonator Trong Trận Chiến" đã chính thức ra mắt!
+Ghi lại những khoảnh khắc hào hùng của Resonator trong trận chiến, rồi gửi ảnh cho Fulmine và C-MOSS để nhận về vô vàn phần thưởng!</t>
         </is>
       </c>
     </row>
@@ -26100,7 +26100,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Lễ Kỷ Niệm Second Coming of Solaris sắp đến, nhưng rắc rối đã ập đến Thế Giới Cube! Vua quỷ bí ẩn Abbowser đã bắt cóc tất cả các Cube và thách thức Chiến Binh Black Cat huyền thoại. "Hãy bước vào thế giới bí ẩn, đối đầu với tay sai của ta, giải cứu bạn bè bị mất tích, và đối mặt với ta trong trận quyết chiến cuối cùng! Nào, sẽ rất thú vị đấy!"</t>
+          <t>Lễ Kỷ Niệm Sự Trở Lại Của Solaris sắp đến, nhưng rắc rối đã ập đến Thế Giới Khối Lập Phương! Vua quỷ bí ẩn Abbowser đã bắt cóc tất cả các Khối Lập Phương và thách thức Chiến Binh Mèo Đen huyền thoại. "Hãy bước vào thế giới bí ẩn, đối đầu với tay sai của ta, giải cứu bạn bè bị mất tích, và đối mặt với ta trong trận quyết chiến cuối cùng! Nào, sẽ rất thú vị đấy!"</t>
         </is>
       </c>
     </row>
@@ -26298,8 +26298,8 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Một thông điệp kỳ lạ thu hút sự chú ý của cậu đến một trò chơi đấu Echoes bí ẩn mang tên "Peaks of Prestige". Người ta nói rằng vô số kẻ thách đấu đã lên đường để giành lấy danh hiệu huyền thoại "Apex Duelist".
-"Vô số Echoes. Chiến thuật vô biên. Cậu có thể là Apex Duelist tiếp theo!"</t>
+          <t>Một thông điệp kỳ lạ thu hút sự chú ý của cậu đến một trò chơi đấu Echo bí ẩn mang tên "Peaks of Prestige". Người ta nói rằng vô số kẻ thách đấu đã lên đường để giành lấy danh hiệu huyền thoại "Apex Duelist".
+"Vô số Echo. Chiến thuật vô biên. Cậu có thể là Apex Duelist tiếp theo!"</t>
         </is>
       </c>
     </row>
@@ -26432,7 +26432,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>"Chào Rover, chào mừng đến với Triển lãm Chụp ảnh Solaris!"
+          <t>"Chào Rover, chào mừng đến với Triển lãm Ảnh Solaris!"
 Hành trình của cậu sẽ diễn ra như thế nào trong thế giới hoàn toàn mới này? Những cảnh sắc mơ ước, những người bạn mong gặp, và những câu chuyện sắp viết nên... ký ức sẽ hiện lên rực rỡ sắc màu, bắt đầu từ đây, từ chính cậu.</t>
         </is>
       </c>
@@ -26695,7 +26695,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Xưởng Vải Dệt Dưới Vực đã động đậy bên dưới những con sóng, sự bất ổn của nó được giới quý tộc và Hội Ánh Sáng âm thầm ghi nhận. Để ngăn chặn sự xáo trộn thêm cho cuộc sống của người dân Ragunna và tránh gây hoang mang không cần thiết, cả hai bên đã tổ chức một cuộc họp kín hiếm có. Trong một động thái chưa từng có, họ đã đạt được đồng thuận: cần tiến hành khảo sát lại toàn bộ cơ sở này để làm cơ sở cho các cuộc thảo luận chung về số phận của Xưởng Vải Dệt và những Echo Chung mà nó lưu giữ. Là người duy nhất trở về từ nơi đó mà không hề hấn gì, cậu chính là lựa chọn tốt nhất để dẫn dắt cuộc thám hiểm này.</t>
+          <t>Xưởng Vải Dệt Dưới Vực đã động đậy bên dưới những con sóng, sự bất ổn của nó được giới quý tộc và Hội Ánh Sáng âm thầm ghi nhận. Để ngăn chặn sự xáo trộn thêm cho cuộc sống của người dân Ragunna và tránh gây hoang mang không cần thiết, cả hai bên đã tổ chức một cuộc họp kín hiếm có. Trong một động thái chưa từng có, họ đã đạt được đồng thuận: cần tiến hành khảo sát lại toàn bộ cơ sở này để làm cơ sở cho các cuộc thảo luận chung về số phận của Xưởng Vải Dệt và những Tiếng Vọng Chung mà nó lưu giữ. Là người duy nhất trở về từ nơi đó mà không hề hấn gì, cậu chính là lựa chọn tốt nhất để dẫn dắt cuộc thám hiểm này.</t>
         </is>
       </c>
     </row>
@@ -26762,7 +26762,7 @@
       <c r="M392" t="inlineStr">
         <is>
           <t>Sự kiện web “Trở Lại Solaris” đã bắt đầu! Tham gia để nhận tới 530 Astrites cùng nhiều phần thưởng khác.
-Invite những người bạn cũ quay lại và cùng hoàn thành nhiệm vụ để nhận Astrites, Shell Credits và nhiều phần thưởng khác! Các Rover quay lại liên kết tài khoản sẽ nhận thêm quà tặng đặc biệt!</t>
+Mời những người bạn cũ quay lại và cùng hoàn thành nhiệm vụ để nhận Astrites, Shell Credits và nhiều phần thưởng khác! Các Vận Mệnh Giả quay lại liên kết tài khoản sẽ nhận thêm quà tặng đặc biệt!</t>
         </is>
       </c>
     </row>
@@ -26829,7 +26829,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Theo lời mời của Iuno, ngươi lên đỉnh Tetragon Temple để cùng nàng ngắm nhìn bầu trời sao.
+          <t>Theo lời mời của Iuno, ngươi lên đỉnh Đền Tetragon để cùng nàng ngắm nhìn bầu trời sao.
 Giữa ánh sao trôi lơ lửng nơi số phận giao hòa với các chòm sao, nàng tiết lộ những bí ẩn và phước lành ẩn chứa trong các pha trăng của Septimont…
 “Ngươi đến từ Huanglong phải không? Hehe, đừng lo. Ta có thể xem trăng theo phong cách Huanglong cho ngươi đấy.”</t>
         </is>
@@ -26896,7 +26896,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Một cánh cổng quen thuộc xuất hiện trên vùng đất Rinascita, kết nối với một thế giới gọi là Somnoire. Những ký ức xưa chôn giấu sâu trong giấc mơ, và chìa khóa khám phá nằm trong tay bạn. Xin đừng quên, chỉ trong giấc mơ mới tìm thấy câu trả lời.</t>
+          <t>Một cánh cổng quen thuộc xuất hiện trên vùng đất Rinascita, nối liền với thế giới mang tên Somnoire. Những ký ức xa xưa chôn sâu trong giấc mơ, và chìa khóa khám phá giờ nằm trong tay ngươi. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.</t>
         </is>
       </c>
     </row>
@@ -26965,7 +26965,7 @@
         <is>
           <t>Maji, ông vua ý tưởng, lại trở lại với chiến dịch mới—
 Lần này, hắn đang bắt kịp làn sóng công nghệ và thử tạo ra trợ lý thông minh riêng, Lollo Genie.
-Tương tác với những Echoes đáng yêu và gửi dữ liệu hành vi của chúng cho Maji để nhận Lollo Stamps và tham gia xổ số hấp dẫn!</t>
+Tương tác với những Echo đáng yêu và gửi dữ liệu hành vi của chúng cho Maji để nhận Lollo Stamps và tham gia xổ số hấp dẫn!</t>
         </is>
       </c>
     </row>
@@ -27164,7 +27164,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>KU-Ryan, một robot của Black Shores, hiện đang cần hỗ trợ thu thập Surveillance Dataset về Hiện Tượng Bị Sóng Xói Mòn tại Septimont. Địa hình hiểm trở đòi hỏi phản xạ nhạy bén và kỹ năng móc treo điêu luyện. Nếu đây là nhiệm vụ hợp gu cậu, hãy tìm gặp hắn để biết thêm chi tiết.</t>
+          <t>KU-Ryan, một robot của Black Shores, hiện đang cần hỗ trợ thu thập Bộ Dữ Liệu Giám Sát về Hiện Tượng Bị Sóng Xói Mòn tại Septimont. Địa hình hiểm trở đòi hỏi phản xạ nhạy bén và kỹ năng móc treo điêu luyện. Nếu đây là nhiệm vụ hợp gu cậu, hãy tìm gặp hắn để biết thêm chi tiết.</t>
         </is>
       </c>
     </row>
@@ -27229,7 +27229,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Rover thân mến, thời gian đổi thưởng của sự kiện giới hạn thời gian {0} sắp kết thúc. Đừng ngần ngại tham gia và nhận phần thưởng sự kiện của bạn nhé. Cảm ơn vì đã ủng hộ!</t>
+          <t>Vận Mệnh Giả thân mến, thời gian đổi thưởng của sự kiện giới hạn thời gian {0} sắp kết thúc. Đừng ngần ngại tham gia và nhận phần thưởng sự kiện của bạn nhé. Cảm ơn vì đã ủng hộ!</t>
         </is>
       </c>
     </row>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Nhờ sự trợ giúp của cậu, Chiến Thuật Mô Phỏng đã đạt được thành công bước đầu. Học viện đã đo được Tính Điều Chỉnh của tần số Discord. Phá vỡ Tính Điều Chỉnh của chúng sẽ là đòn chí mạng...</t>
+          <t>Nhờ sự trợ giúp của cậu, Chiến Thuật Mô Phỏng đã đạt được thành công bước đầu. Học viện đã đo được Tính Điều Chỉnh của tần số Tacet Discord. Phá vỡ Tính Điều Chỉnh của chúng sẽ là đòn chí mạng...</t>
         </is>
       </c>
     </row>
@@ -27360,8 +27360,8 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Sau khi khủng hoảng vòng lặp của Honami City kết thúc, Namipon từ Quán cà phê Shashou liên lạc nhờ cậu và Chisa giúp điều tra hàng loạt hiện tượng kỳ lạ trên khắp Honami.
-Assist Namipon trong cuộc điều tra đồng thời thu thập vật liệu để cải tạo Quán cà phê Shashou.</t>
+          <t>Sau khi khủng hoảng vòng lặp của Thành phố Honami kết thúc, Namipon từ Quán cà phê Shashou liên lạc nhờ cậu và Chisa giúp điều tra hàng loạt hiện tượng kỳ lạ trên khắp Honami.
+Hỗ trợ Namipon trong cuộc điều tra đồng thời thu thập vật liệu để cải tạo Quán cà phê Shashou.</t>
         </is>
       </c>
     </row>
@@ -27572,7 +27572,7 @@
       <c r="M404" t="inlineStr">
         <is>
           <t>Sự kiện web “Trở Lại Solaris” đã bắt đầu! Tham gia để nhận tới 530 Astrites.
-Invite những người bạn cũ quay lại và cùng hoàn thành nhiệm vụ để nhận Astrites, Shell Credits và nhiều phần thưởng khác! Các Rover quay lại liên kết tài khoản sẽ nhận thêm quà tặng đặc biệt!</t>
+Mời những người bạn cũ quay lại và cùng hoàn thành nhiệm vụ để nhận Astrites, Shell Credits và nhiều phần thưởng khác! Các Vận Mệnh Giả quay lại liên kết tài khoản sẽ nhận thêm quà tặng đặc biệt!</t>
         </is>
       </c>
     </row>
@@ -27638,7 +27638,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Câu lạc bộ fan "Peaks of Prestige" của Startorch Academy đang đối mặt với cuộc khủng hoảng lớn nhất từ trước đến nay. Nhưng mối đe dọa không đến từ bên ngoài, mà từ... chính những giáo viên luôn tự nhận là vì lợi ích của học sinh.
+          <t>Câu lạc bộ fan "Đỉnh Cao Danh Vọng" của Học viện Startorch đang đối mặt với cuộc khủng hoảng lớn nhất từ trước đến nay. Nhưng mối đe dọa không đến từ bên ngoài, mà từ... chính những giáo viên luôn tự nhận là vì lợi ích của học sinh.
 Giờ đây, số phận của câu lạc bộ hoàn toàn nằm trong tay cậu. Hãy giành lấy chiến thắng và đập tan bóng tối đang phủ xuống!</t>
         </is>
       </c>
@@ -27705,7 +27705,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Câu lạc bộ fan "Peaks of Prestige" của Startorch Academy đang đối mặt với cuộc khủng hoảng lớn nhất từ trước đến nay. Nhưng mối đe dọa không đến từ bên ngoài, mà từ... chính những giáo viên luôn tự nhận là vì lợi ích của học sinh.
+          <t>Câu lạc bộ fan "Đỉnh Cao Danh Vọng" của Học viện Startorch đang đối mặt với cuộc khủng hoảng lớn nhất từ trước đến nay. Nhưng mối đe dọa không đến từ bên ngoài, mà từ... chính những giáo viên luôn tự nhận là vì lợi ích của học sinh.
 Giờ đây, số phận của câu lạc bộ hoàn toàn nằm trong tay cậu. Hãy giành lấy chiến thắng và đập tan bóng tối đang phủ xuống!</t>
         </is>
       </c>
@@ -27836,7 +27836,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Lollo Logistics một lần nữa hợp tác với Pioneer Association hân hạnh giới thiệu chiến dịch phong phú: Beyond the Waves! Chỉ cần tải Nhật Ký Phiêu Lưu của cậu lên chiếc xe chuyển phát này, và cậu sẽ nhận được "Gói Phiêu Lưu" tương ứng với địa điểm đó, chứa đầy bất ngờ!</t>
+          <t>Lollo Logistics một lần nữa hợp tác với Hiệp Hội Tiên Phong hân hạnh giới thiệu chiến dịch phong phú: Beyond the Waves! Chỉ cần tải Nhật Ký Phiêu Lưu của cậu lên chiếc xe chuyển phát này, và cậu sẽ nhận được "Gói Phiêu Lưu" tương ứng với địa điểm đó, chứa đầy bất ngờ!</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Challenge Độ Khó High&lt;/color&gt;
+          <t>&lt;color=Highlight&gt;Thử Thách Độ Khó Cao&lt;/color&gt;
 Trong cơ sở dữ liệu của Spacetrek Collective, những cuộc tấn công và phòng thủ vô hình diễn ra hàng ngày. Hãy tìm ra ác ý ẩn sâu trong ma trận và xóa bỏ nó.</t>
         </is>
       </c>
@@ -28101,8 +28101,8 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;(Chương III Nhiệm vụ Main hiện đã mở khóa, người chơi đủ điều kiện có thể trải nghiệm chương này sớm.)&lt;/color&gt;
-Hỡi Rover được dòng chảy dẫn lối, ngươi đã chinh phục những đỉnh cao ở Jinzhou và lắng nghe sóng vỗ vào Bờ Đen. Ngươi đã vượt qua bão tố, nghe thấy bản chất kép của niềm tin Ragunna, và nếm trải vinh quang trong đấu trường Septimont. Giờ đây, con đường đến vùng biên giới băng giá mở ra tại Honami City. Đã đến lúc tiến về Lahai-Roi.</t>
+          <t>&lt;color=Highlight&gt;(Chương III Nhiệm vụ Chính hiện đã mở khóa, người chơi đủ điều kiện có thể trải nghiệm chương này sớm.)&lt;/color&gt;
+Hỡi Vận Mệnh Giả được dòng chảy dẫn lối, ngươi đã chinh phục những đỉnh cao ở Jinzhou và lắng nghe sóng vỗ vào Bờ Đen. Ngươi đã vượt qua bão tố, nghe thấy bản chất kép của niềm tin Ragunna, và nếm trải vinh quang trong đấu trường Septimont. Giờ đây, con đường đến vùng biên giới băng giá mở ra tại Thành phố Honami. Đã đến lúc tiến về Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -28167,7 +28167,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>&lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity30/BeginnerSupport/GuideMain/T_BeginnerTxtArrow.T_BeginnerTxtArrow/&gt; Trong sự kiện, bạn có thể chiêu mộ Resonators hỗ trợ và mở khóa nhiều phần thưởng hấp dẫn khi &lt;color=#f6de91&gt;SOL3 Giai đoạn&lt;/color&gt; tăng lên.</t>
+          <t>&lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity30/BeginnerSupport/GuideMain/T_BeginnerTxtArrow.T_BeginnerTxtArrow/&gt; Trong sự kiện, bạn có thể chiêu mộ Resonator hỗ trợ và mở khóa nhiều phần thưởng hấp dẫn khi &lt;color=#f6de91&gt;Giai Đoạn SOL3&lt;/color&gt; tăng lên.</t>
         </is>
       </c>
     </row>
@@ -28567,7 +28567,7 @@
       <c r="M419" t="inlineStr">
         <is>
           <t>Dù có thể mờ ảo và xanh mướt, những ngày tháng học trò vẫn luôn lấp lánh như viên ngọc trong dòng sông ký ức. Những câu chuyện ấy trôi dạt giữa các vì sao, là người bạn đồng hành bên ta trong mỗi đêm tĩnh lặng.
-Khi New Solar Celebration bắt đầu, những câu chuyện nhỏ mới lại nở rộ giữa bạn và những người bạn của mình...</t>
+Khi Lễ Hội Mặt Trời Mới bắt đầu, những câu chuyện nhỏ mới lại nở rộ giữa bạn và những người bạn của mình...</t>
         </is>
       </c>
     </row>
@@ -28697,7 +28697,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Gần đây, "Stellar Orbit Beats" đang làm mưa làm gió tại Mind Dive Arcade! Đây chính thức là trò chơi giải trí yêu thích của mọi người ở Academy. Rảnh rỗi giữa giờ học? Rủ bạn bè cùng hòa mình vào nhịp điệu xuyên vũ trụ nào!</t>
+          <t>Gần đây, "Stellar Orbit Beats" đang làm mưa làm gió tại Mind Dive Arcade! Đây chính thức là trò chơi giải trí yêu thích của mọi người ở Học Viện. Rảnh rỗi giữa giờ học? Rủ bạn bè cùng hòa mình vào nhịp điệu xuyên vũ trụ nào!</t>
         </is>
       </c>
     </row>
@@ -28763,7 +28763,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Rover thân mến,
+          <t>Vận Mệnh Giả thân mến,
 Bạn có một chỉnh sửa thuộc tính phụ cần hoàn tất. Thay đổi này sẽ được lưu trên máy chủ trong 30 ngày. Hãy xác nhận quyết định của bạn càng sớm càng tốt. (Thông báo này chỉ nhằm mục đích thông tin)</t>
         </is>
       </c>
@@ -28829,7 +28829,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Những Knights of the Wild, như mọi người vẫn gọi, là những Mechascout lang thang khắp vùng Lahai-Roi, thề bảo vệ những ai gặp nguy hiểm. Nhưng lần này, chính các Hiệp Sĩ lại là những người cần sự trợ giúp.</t>
+          <t>Những Hiệp Sĩ Hoang Dã, như mọi người vẫn gọi, là những Mechascout lang thang khắp vùng Lahai-Roi, thề bảo vệ những ai gặp nguy hiểm. Nhưng lần này, chính các Hiệp Sĩ lại là những người cần sự trợ giúp.</t>
         </is>
       </c>
     </row>
@@ -29089,7 +29089,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Lễ kỷ niệm 2 năm Second Coming of Solaris chính thức khởi động! Năm nay, sự kiện được đồng tổ chức bởi bốn đối tác: Spacetrek Collective, Startorch Academy, Lollo Logistics và Pioneer Association. Hãy tham gia và nhận về kho phần thưởng hấp dẫn!</t>
+          <t>Lễ kỷ niệm 2 năm Sự Trở Lại Của Solaris chính thức khởi động! Năm nay, sự kiện được đồng tổ chức bởi bốn đối tác: Spacetrek Collective, Học viện Startorch, Lollo Logistics và Hiệp hội Pioneer. Hãy tham gia và nhận về kho phần thưởng hấp dẫn!</t>
         </is>
       </c>
     </row>
@@ -29221,7 +29221,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Lollo Logistics một lần nữa hợp tác với Pioneer Association hân hạnh giới thiệu chiến dịch phong phú: Beyond the Waves! Upload Nhật Ký Phiêu Lưu nhận được sau khi hoàn thành nhiệm vụ hằng ngày, và cậu sẽ nhận được "Gói Phiêu Lưu" tương ứng với địa điểm đó, chứa đầy bất ngờ!</t>
+          <t>Lollo Logistics một lần nữa hợp tác với Hiệp Hội Tiên Phong hân hạnh giới thiệu chiến dịch phong phú: Beyond the Waves! Tải lên Nhật Ký Phiêu Lưu nhận được sau khi hoàn thành nhiệm vụ hằng ngày, và cậu sẽ nhận được "Gói Phiêu Lưu" tương ứng với địa điểm đó, chứa đầy bất ngờ!</t>
         </is>
       </c>
     </row>
@@ -29355,7 +29355,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Rover thân mến, thời gian nhận phần thưởng giới hạn của sự kiện {0} sắp kết thúc. Đừng ngần ngại tham gia và nhận phần thưởng sự kiện của bạn nhé. Cảm ơn vì đã ủng hộ!</t>
+          <t>Vận Mệnh Giả thân mến, thời gian nhận phần thưởng giới hạn của sự kiện {0} sắp kết thúc. Đừng ngần ngại tham gia và nhận phần thưởng sự kiện của bạn nhé. Cảm ơn vì đã ủng hộ!</t>
         </is>
       </c>
     </row>
@@ -29420,7 +29420,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Event hợp tác Anniversary 30 năm Resident Evil, Angry Birds và Kaiju Không. 8. Hoàn thành nhiệm vụ trong Event Hợp tác để nhận được Livery Hợp tác tương ứng và nhiều loại Vật liệu tăng cấp.</t>
+          <t>Sự kiện hợp tác Kỷ niệm 30 năm Resident Evil, Angry Birds và Kaiju No. 8. Hoàn thành nhiệm vụ trong Sự kiện Hợp tác để nhận được Livery Hợp tác tương ứng và nhiều loại Vật liệu tăng cấp.</t>
         </is>
       </c>
     </row>
@@ -29485,7 +29485,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>"PRAGMATA," "Riders Republic," và "HAIKYU!!" (anime) Event Cộng tác. Hoàn thành nhiệm vụ trong Event Cộng tác để nhận được Livery Cộng tác tương ứng và nhiều loại Vật liệu tăng cấp.</t>
+          <t>"PRAGMATA," "Riders Republic," và "HAIKYU!!" (anime) Sự kiện Cộng tác. Hoàn thành nhiệm vụ trong Sự kiện Cộng tác để nhận được Livery Cộng tác tương ứng và nhiều loại Vật liệu tăng cấp.</t>
         </is>
       </c>
     </row>
@@ -30265,7 +30265,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Này, cậu{Male= trai;Female= gái} trẻ. Chắc hẳn cậu còn nhiều việc quan trọng hơn phải làm. Đừng để ông già như tôi cản đường. Hãy đi và hoàn thành nhiệm vụ của mình với quyết tâm nhé.</t>
+          <t>Này, cậu{Male=man;Female=lady} trẻ. Chắc hẳn cậu còn nhiều việc quan trọng hơn phải làm. Đừng để ông già như tôi cản đường. Hãy đi và hoàn thành nhiệm vụ của mình với quyết tâm nhé.</t>
         </is>
       </c>
     </row>
@@ -30850,7 +30850,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Speaking of which... tình trạng của Sentinel chúng ta đang xấu đi. Gần đây, nó thường phải nằm lại Mianloong Chamber lâu hơn, gần như quay về trạng thái "ngủ đông" thường xuyên hơn.</t>
+          <t>Nhắc mới nhớ... tình trạng của Sentinel chúng ta đang xấu đi. Gần đây, nó thường phải nằm lại Mianloong Chamber lâu hơn, gần như quay về trạng thái "ngủ đông" thường xuyên hơn.</t>
         </is>
       </c>
     </row>
@@ -31175,7 +31175,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Cô ấy lớn lên với gánh nặng trách nhiệm khổng lồ, bị ép phải kìm Dodgen bản chất thật từ khi còn nhỏ. Nghĩ lại mà xem, Jinhsi chỉ là một cô bé mới lớn khi trở thành Magistrate...</t>
+          <t>Cô ấy lớn lên với gánh nặng trách nhiệm khổng lồ, bị ép phải kìm nén bản chất thật từ khi còn nhỏ. Nghĩ lại mà xem, Jinhsi chỉ là một cô bé mới lớn khi trở thành Magistrate...</t>
         </is>
       </c>
     </row>
@@ -31500,7 +31500,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>...Ta đang theo đuổi trái tim của chính mình khi còn là Jinhsi: cô gái từng cười vui sướng khi cảm nhận tuyết từ Núi Firmament trên gương mặt.</t>
+          <t>...Ta đang theo đuổi trái tim của chính mình khi còn là Jinhsi: The girl who used to laugh with pure joy as she felt the snow from Mt. Firmament on her face.</t>
         </is>
       </c>
     </row>
@@ -31890,7 +31890,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Nhưng số phận không thể cưỡng lại. Bọn Fractsidus đã âm mưu hại ta. Giờ đây, vết thương ngày càng trầm trọng... Mianloong Chamber không còn khả năng kéo dài sinh mệnh nữa.</t>
+          <t>Nhưng số phận không thể cưỡng lại. Bọn Fractsidus đã âm mưu hại ta. Giờ đây, vết thương ngày càng trầm trọng... Phòng Mianloong không còn khả năng kéo dài sinh mệnh nữa.</t>
         </is>
       </c>
     </row>
@@ -31955,7 +31955,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Kể từ khi một Rover giáng lâm tại Núi Firmament, sử dụng sức mạnh của Temporal Mandate để đẩy lùi lũ Tacet Discord, thời gian tại nơi này đã rơi vào hỗn loạn. Số phận của Jinzhou đã được định đoạt từ giây phút đó.</t>
+          <t>Kể từ khi một Vận Mệnh Giả giáng lâm tại Núi Firmament, sử dụng sức mạnh của Temporal Mandate để đẩy lùi lũ Tacet Discord, thời gian tại nơi này đã rơi vào hỗn loạn. Số phận của Jinzhou đã được định đoạt từ giây phút đó.</t>
         </is>
       </c>
     </row>
@@ -32345,7 +32345,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Tôi chỉ có thể mang sức mạnh của ngài trong khoảnh khắc ngắn ngủi... Nhưng như thế là đủ để bảo đảm một tương lai tốt đẹp hơn cho Jinzhou, bất chấp mọi dự đoán của ngài. Và tôi có thể bảo vệ ngài an toàn.</t>
+          <t>Tôi chỉ có thể mang sức mạnh của bạn trong khoảnh khắc ngắn ngủi... Nhưng như thế là đủ để bảo đảm một tương lai tốt đẹp hơn cho Jinzhou, bất chấp mọi dự đoán của bạn. Và tôi có thể bảo vệ bạn an toàn.</t>
         </is>
       </c>
     </row>
@@ -32865,7 +32865,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Hồng Trấn là vị trí then chốt, nối liền các khu vực trên núi Cương Thành. Với việc Fractsidus đang nhắm vào chúng ta, chúng sẽ không bỏ lỡ bất kỳ cơ hội nào để chặn đường.</t>
+          <t>Hongzhen là vị trí then chốt, nối liền các khu vực trên núi Cương Thành. Với việc Fractsidus đang nhắm vào chúng ta, chúng sẽ không bỏ lỡ bất kỳ cơ hội nào để chặn đường.</t>
         </is>
       </c>
     </row>
@@ -32995,7 +32995,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Tại Tòa Thị Chính, Sanhua tiết lộ rằng Quan Phủ đã lên Núi Thiên Cung vài ngày trước vì lo lắng cho sự an toàn của Sentinel. Bạn bày tỏ ý định đi theo, và Sanhua đề nghị liên lạc với một người dẫn đường cho chuyến hành trình đầy hiểm nguy. Cô ấy sắp xếp một cuộc gặp với Wayfinder tại Bãi Lầy Whining Aix.</t>
+          <t>Tại Tòa Thị Chính, Sanhua tiết lộ rằng Quan Phủ đã lên Núi Thiên Cung vài ngày trước vì lo lắng cho sự an toàn của Sentinel. Bạn bày tỏ ý định đi theo, và Sanhua đề nghị liên lạc với một người dẫn đường cho chuyến hành trình đầy hiểm nguy. Cô ấy sắp xếp một cuộc gặp với Wayfinder tại Whining Aix's Mire.</t>
         </is>
       </c>
     </row>
@@ -33125,7 +33125,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Khi đặt chân lên Núi Thiên Cung, cậu nhận ra dòng thời gian ở đây đã mất kiểm soát, nhiều sinh vật trở thành nạn nhân của nó. Nếu rời đi bây giờ, tuổi tác của cậu có thể thay đổi khó lường. Changli phát hiện Terminal của mình không hoạt động và đề nghị nhanh chóng đến Hồng Trấn – thị trấn mà Jinhsi nhất định phải ghé qua trong hành trình tìm kiếm Sentinel.</t>
+          <t>Khi đặt chân lên Núi Thiên Cung, cậu nhận ra dòng thời gian ở đây đã mất kiểm soát, nhiều sinh vật trở thành nạn nhân của nó. Nếu rời đi bây giờ, tuổi tác của cậu có thể thay đổi khó lường. Changli phát hiện Thiết bị đầu cuối của mình không hoạt động và đề nghị nhanh chóng đến Hongzhen – thị trấn mà Jinhsi nhất định phải ghé qua trong hành trình tìm kiếm Sentinel.</t>
         </is>
       </c>
     </row>
@@ -33255,7 +33255,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Bạn biết được Sentinel có thể đang bị giam cầm tại nơi an nghỉ của nó—Mianloong Chamber. Cuộc xâm lăng của Fractsidus đã kích hoạt hệ thống phòng thủ do Court of Savantae xây dựng, phong ấn căn phòng. Jinhsi đã rời đi ngay trước đó để đến Đèo Truthseeker lấy Cipher Key cần thiết để mở phong ấn. Bạn và Changli tiếp tục truy tìm dấu vết của cô.</t>
+          <t>Bạn biết được Sentinel có thể đang bị giam cầm tại nơi an nghỉ của nó—Phòng Mianloong. Cuộc xâm lăng của Fractsidus đã kích hoạt hệ thống phòng thủ do Court of Savantae xây dựng, phong ấn căn phòng. Jinhsi đã rời đi ngay trước đó để đến Đèo Truthseeker lấy Chìa Khóa Mật Mã cần thiết để mở phong ấn. Bạn và Changli tiếp tục truy tìm dấu vết của cô.</t>
         </is>
       </c>
     </row>
@@ -33645,7 +33645,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Khi bụi mù lắng xuống, Jué gặp ngươi như đã hứa. Ngươi biết được mình từng là sư phụ của Jué và cùng nó xây dựng Jinzhou. Jué nhận thấy điều gì đó bất thường ở Echo của ngươi ngay khi Abby xuất hiện và cả hai đối đầu nhau. Ngay cả Jué cũng không rõ nguồn gốc của Abby, nhưng gợi ý rằng ngươi nên đến Black Shores, nơi khởi đầu hành trình của ngươi ở thế giới này.</t>
+          <t>Khi bụi mù lắng xuống, Jué gặp ngươi như đã hứa. Ngươi biết được mình từng là sư phụ của Jué và cùng nó xây dựng Jinzhou. Jué nhận thấy điều gì đó bất thường ở Tổ Tacet của ngươi ngay khi Abby xuất hiện và cả hai đối đầu nhau. Ngay cả Jué cũng không rõ nguồn gốc của Abby, nhưng gợi ý rằng ngươi nên đến Black Shores, nơi khởi đầu hành trình của ngươi ở thế giới này.</t>
         </is>
       </c>
     </row>
@@ -33905,7 +33905,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Khi chúng ta tiến về Núi Firmament, {PlayerName} kể về một giấc mơ kỳ lạ mà {Male=cậu ấy;Female=cô ấy} từng mơ. Có lẽ đó là hồi ức đã mất của {Male=cậu ấy;Female=cô ấy}.</t>
+          <t>Khi chúng ta tiến về Núi Firmament, {PlayerName} kể về một giấc mơ kỳ lạ mà {Male=his;Female=her} từng mơ. Có lẽ đó là hồi ức đã mất của {Male=his;Female=her}.</t>
         </is>
       </c>
     </row>
